--- a/2026/3t/SEPTIEMBRE/ALBARANES/COMPARATIVA PRECIOS LA MINA CHAMARTIN SEPTIEMBRE 2026.xlsx
+++ b/2026/3t/SEPTIEMBRE/ALBARANES/COMPARATIVA PRECIOS LA MINA CHAMARTIN SEPTIEMBRE 2026.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="COMPARATIVA PRECIOS" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'COMPARATIVA PRECIOS'!$A$55:$K$362</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'COMPARATIVA PRECIOS'!$A$55:$K$364</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -568,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K362"/>
+  <dimension ref="A1:K364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="C5" s="6">
-        <f>COUNTIF($I$56:$I$362,"SUBE")</f>
+        <f>COUNTIF($I$56:$I$364,"SUBE")</f>
         <v/>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="C6" s="6">
-        <f>COUNTIF($I$56:$I$362,"BAJA")</f>
+        <f>COUNTIF($I$56:$I$364,"BAJA")</f>
         <v/>
       </c>
     </row>
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="C7" s="6">
-        <f>COUNTIF($I$56:$I$362,"IGUAL")</f>
+        <f>COUNTIF($I$56:$I$364,"IGUAL")</f>
         <v/>
       </c>
     </row>
@@ -655,7 +655,7 @@
         </is>
       </c>
       <c r="C8" s="6">
-        <f>COUNTIF($I$56:$I$362,"NUEVO")</f>
+        <f>COUNTIF($I$56:$I$364,"NUEVO")</f>
         <v/>
       </c>
     </row>
@@ -666,7 +666,7 @@
         </is>
       </c>
       <c r="C9" s="6">
-        <f>COUNTIF($I$56:$I$362,"SIN COMPRA")</f>
+        <f>COUNTIF($I$56:$I$364,"SIN COMPRA")</f>
         <v/>
       </c>
     </row>
@@ -736,23 +736,23 @@
     </row>
     <row r="13">
       <c r="A13" s="5">
-        <f>A210</f>
+        <f>A211</f>
         <v/>
       </c>
       <c r="B13" s="5">
-        <f>B210</f>
+        <f>B211</f>
         <v/>
       </c>
       <c r="C13" s="11">
-        <f>F210</f>
+        <f>F211</f>
         <v/>
       </c>
       <c r="D13" s="11">
-        <f>E210</f>
+        <f>E211</f>
         <v/>
       </c>
       <c r="E13" s="12">
-        <f>H210</f>
+        <f>H211</f>
         <v/>
       </c>
       <c r="G13" s="5">
@@ -778,65 +778,65 @@
     </row>
     <row r="14">
       <c r="A14" s="5">
-        <f>A181</f>
+        <f>A182</f>
         <v/>
       </c>
       <c r="B14" s="5">
-        <f>B181</f>
+        <f>B182</f>
         <v/>
       </c>
       <c r="C14" s="11">
-        <f>F181</f>
+        <f>F182</f>
         <v/>
       </c>
       <c r="D14" s="11">
-        <f>E181</f>
+        <f>E182</f>
         <v/>
       </c>
       <c r="E14" s="12">
-        <f>H181</f>
+        <f>H182</f>
         <v/>
       </c>
       <c r="G14" s="5">
-        <f>A197</f>
+        <f>A198</f>
         <v/>
       </c>
       <c r="H14" s="5">
-        <f>B197</f>
+        <f>B198</f>
         <v/>
       </c>
       <c r="I14" s="11">
-        <f>F197</f>
+        <f>F198</f>
         <v/>
       </c>
       <c r="J14" s="11">
-        <f>E197</f>
+        <f>E198</f>
         <v/>
       </c>
       <c r="K14" s="13">
-        <f>H197</f>
+        <f>H198</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5">
-        <f>A201</f>
+        <f>A202</f>
         <v/>
       </c>
       <c r="B15" s="5">
-        <f>B201</f>
+        <f>B202</f>
         <v/>
       </c>
       <c r="C15" s="11">
-        <f>F201</f>
+        <f>F202</f>
         <v/>
       </c>
       <c r="D15" s="11">
-        <f>E201</f>
+        <f>E202</f>
         <v/>
       </c>
       <c r="E15" s="12">
-        <f>H201</f>
+        <f>H202</f>
         <v/>
       </c>
       <c r="G15" s="5">
@@ -862,85 +862,85 @@
     </row>
     <row r="16">
       <c r="A16" s="5">
-        <f>A261</f>
+        <f>A262</f>
         <v/>
       </c>
       <c r="B16" s="5">
-        <f>B261</f>
+        <f>B262</f>
         <v/>
       </c>
       <c r="C16" s="11">
-        <f>F261</f>
+        <f>F262</f>
         <v/>
       </c>
       <c r="D16" s="11">
-        <f>E261</f>
+        <f>E262</f>
         <v/>
       </c>
       <c r="E16" s="12">
-        <f>H261</f>
+        <f>H262</f>
         <v/>
       </c>
       <c r="G16" s="5">
-        <f>A236</f>
+        <f>A237</f>
         <v/>
       </c>
       <c r="H16" s="5">
-        <f>B236</f>
+        <f>B237</f>
         <v/>
       </c>
       <c r="I16" s="11">
-        <f>F236</f>
+        <f>F237</f>
         <v/>
       </c>
       <c r="J16" s="11">
-        <f>E236</f>
+        <f>E237</f>
         <v/>
       </c>
       <c r="K16" s="13">
-        <f>H236</f>
+        <f>H237</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5">
-        <f>A178</f>
+        <f>A179</f>
         <v/>
       </c>
       <c r="B17" s="5">
-        <f>B178</f>
+        <f>B179</f>
         <v/>
       </c>
       <c r="C17" s="11">
-        <f>F178</f>
+        <f>F179</f>
         <v/>
       </c>
       <c r="D17" s="11">
-        <f>E178</f>
+        <f>E179</f>
         <v/>
       </c>
       <c r="E17" s="12">
-        <f>H178</f>
+        <f>H179</f>
         <v/>
       </c>
       <c r="G17" s="5">
-        <f>A339</f>
+        <f>A340</f>
         <v/>
       </c>
       <c r="H17" s="5">
-        <f>B339</f>
+        <f>B340</f>
         <v/>
       </c>
       <c r="I17" s="11">
-        <f>F339</f>
+        <f>F340</f>
         <v/>
       </c>
       <c r="J17" s="11">
-        <f>E339</f>
+        <f>E340</f>
         <v/>
       </c>
       <c r="K17" s="13">
-        <f>H339</f>
+        <f>H340</f>
         <v/>
       </c>
     </row>
@@ -966,23 +966,23 @@
         <v/>
       </c>
       <c r="G18" s="5">
-        <f>A232</f>
+        <f>A233</f>
         <v/>
       </c>
       <c r="H18" s="5">
-        <f>B232</f>
+        <f>B233</f>
         <v/>
       </c>
       <c r="I18" s="11">
-        <f>F232</f>
+        <f>F233</f>
         <v/>
       </c>
       <c r="J18" s="11">
-        <f>E232</f>
+        <f>E233</f>
         <v/>
       </c>
       <c r="K18" s="13">
-        <f>H232</f>
+        <f>H233</f>
         <v/>
       </c>
     </row>
@@ -1030,23 +1030,23 @@
     </row>
     <row r="20">
       <c r="A20" s="5">
-        <f>A199</f>
+        <f>A200</f>
         <v/>
       </c>
       <c r="B20" s="5">
-        <f>B199</f>
+        <f>B200</f>
         <v/>
       </c>
       <c r="C20" s="11">
-        <f>F199</f>
+        <f>F200</f>
         <v/>
       </c>
       <c r="D20" s="11">
-        <f>E199</f>
+        <f>E200</f>
         <v/>
       </c>
       <c r="E20" s="12">
-        <f>H199</f>
+        <f>H200</f>
         <v/>
       </c>
     </row>
@@ -1074,45 +1074,45 @@
     </row>
     <row r="22">
       <c r="A22" s="5">
-        <f>A324</f>
+        <f>A325</f>
         <v/>
       </c>
       <c r="B22" s="5">
-        <f>B324</f>
+        <f>B325</f>
         <v/>
       </c>
       <c r="C22" s="11">
-        <f>F324</f>
+        <f>F325</f>
         <v/>
       </c>
       <c r="D22" s="11">
-        <f>E324</f>
+        <f>E325</f>
         <v/>
       </c>
       <c r="E22" s="12">
-        <f>H324</f>
+        <f>H325</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5">
-        <f>A262</f>
+        <f>A263</f>
         <v/>
       </c>
       <c r="B23" s="5">
-        <f>B262</f>
+        <f>B263</f>
         <v/>
       </c>
       <c r="C23" s="11">
-        <f>F262</f>
+        <f>F263</f>
         <v/>
       </c>
       <c r="D23" s="11">
-        <f>E262</f>
+        <f>E263</f>
         <v/>
       </c>
       <c r="E23" s="12">
-        <f>H262</f>
+        <f>H263</f>
         <v/>
       </c>
     </row>
@@ -1184,23 +1184,23 @@
     </row>
     <row r="27">
       <c r="A27" s="5">
-        <f>A344</f>
+        <f>A345</f>
         <v/>
       </c>
       <c r="B27" s="5">
-        <f>B344</f>
+        <f>B345</f>
         <v/>
       </c>
       <c r="C27" s="11">
-        <f>F344</f>
+        <f>F345</f>
         <v/>
       </c>
       <c r="D27" s="11">
-        <f>E344</f>
+        <f>E345</f>
         <v/>
       </c>
       <c r="E27" s="12">
-        <f>H344</f>
+        <f>H345</f>
         <v/>
       </c>
     </row>
@@ -6420,18 +6420,18 @@
     <row r="167">
       <c r="A167" s="5" t="inlineStr">
         <is>
-          <t>MAKRO</t>
+          <t>MAHOU</t>
         </is>
       </c>
       <c r="B167" s="5" t="inlineStr">
         <is>
-          <t>AGUACATE PREMADURO MC 1KG</t>
+          <t>MAHOU CLASICA DUOTANK 1L</t>
         </is>
       </c>
       <c r="C167" s="11" t="n"/>
       <c r="D167" s="11" t="n"/>
       <c r="E167" s="11" t="n">
-        <v>6.25</v>
+        <v>3.9</v>
       </c>
       <c r="F167" s="11">
         <f>IF(D167&lt;&gt;"",D167,IF(C167&lt;&gt;"",C167,""))</f>
@@ -6455,7 +6455,7 @@
       </c>
       <c r="K167" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Precio estimado (albaranes sin valorar): el de la última carga facturada por Mahou. Más 0,10 €/l de impuesto especial de la cerveza (total 4,00 €/l)</t>
         </is>
       </c>
     </row>
@@ -6467,13 +6467,13 @@
       </c>
       <c r="B168" s="5" t="inlineStr">
         <is>
-          <t>AGUACATE PREMADURO MC C-12/16 4KG</t>
+          <t>AGUACATE PREMADURO MC 1KG</t>
         </is>
       </c>
       <c r="C168" s="11" t="n"/>
       <c r="D168" s="11" t="n"/>
       <c r="E168" s="11" t="n">
-        <v>22.72</v>
+        <v>6.25</v>
       </c>
       <c r="F168" s="11">
         <f>IF(D168&lt;&gt;"",D168,IF(C168&lt;&gt;"",C168,""))</f>
@@ -6497,7 +6497,7 @@
       </c>
       <c r="K168" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 21,77 / 22,72</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -6509,13 +6509,13 @@
       </c>
       <c r="B169" s="5" t="inlineStr">
         <is>
-          <t>AJO BLANCO PELADO MC BL 1KG</t>
+          <t>AGUACATE PREMADURO MC C-12/16 4KG</t>
         </is>
       </c>
       <c r="C169" s="11" t="n"/>
       <c r="D169" s="11" t="n"/>
       <c r="E169" s="11" t="n">
-        <v>5.39</v>
+        <v>22.72</v>
       </c>
       <c r="F169" s="11">
         <f>IF(D169&lt;&gt;"",D169,IF(C169&lt;&gt;"",C169,""))</f>
@@ -6539,7 +6539,7 @@
       </c>
       <c r="K169" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 5,07 / 5,39</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 21,77 / 22,72</t>
         </is>
       </c>
     </row>
@@ -6551,13 +6551,13 @@
       </c>
       <c r="B170" s="5" t="inlineStr">
         <is>
-          <t>ALBAHACA MC BJ 125G</t>
+          <t>AJO BLANCO PELADO MC BL 1KG</t>
         </is>
       </c>
       <c r="C170" s="11" t="n"/>
       <c r="D170" s="11" t="n"/>
       <c r="E170" s="11" t="n">
-        <v>3.47</v>
+        <v>5.39</v>
       </c>
       <c r="F170" s="11">
         <f>IF(D170&lt;&gt;"",D170,IF(C170&lt;&gt;"",C170,""))</f>
@@ -6581,7 +6581,7 @@
       </c>
       <c r="K170" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 5,07 / 5,39</t>
         </is>
       </c>
     </row>
@@ -6593,13 +6593,13 @@
       </c>
       <c r="B171" s="5" t="inlineStr">
         <is>
-          <t>ARROZ LARGO MC 1KG (PACK 10)</t>
+          <t>ALBAHACA MC BJ 125G</t>
         </is>
       </c>
       <c r="C171" s="11" t="n"/>
       <c r="D171" s="11" t="n"/>
       <c r="E171" s="11" t="n">
-        <v>1.39</v>
+        <v>3.47</v>
       </c>
       <c r="F171" s="11">
         <f>IF(D171&lt;&gt;"",D171,IF(C171&lt;&gt;"",C171,""))</f>
@@ -6621,7 +6621,11 @@
         <f>IF(AND(C171&lt;&gt;"",D171&lt;&gt;""),IF(C171=0,"",D171/C171-1),"")</f>
         <v/>
       </c>
-      <c r="K171" s="5" t="n"/>
+      <c r="K171" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="5" t="inlineStr">
@@ -6631,13 +6635,13 @@
       </c>
       <c r="B172" s="5" t="inlineStr">
         <is>
-          <t>AZUCAR MORENO ACOR 1KG</t>
+          <t>ARROZ LARGO MC 1KG (PACK 10)</t>
         </is>
       </c>
       <c r="C172" s="11" t="n"/>
       <c r="D172" s="11" t="n"/>
       <c r="E172" s="11" t="n">
-        <v>2.3</v>
+        <v>1.39</v>
       </c>
       <c r="F172" s="11">
         <f>IF(D172&lt;&gt;"",D172,IF(C172&lt;&gt;"",C172,""))</f>
@@ -6669,13 +6673,13 @@
       </c>
       <c r="B173" s="5" t="inlineStr">
         <is>
-          <t>BAYETA MPRO ROLLO PUNTO AZUL 3KG</t>
+          <t>AZUCAR MORENO ACOR 1KG</t>
         </is>
       </c>
       <c r="C173" s="11" t="n"/>
       <c r="D173" s="11" t="n"/>
       <c r="E173" s="11" t="n">
-        <v>18.47</v>
+        <v>2.3</v>
       </c>
       <c r="F173" s="11">
         <f>IF(D173&lt;&gt;"",D173,IF(C173&lt;&gt;"",C173,""))</f>
@@ -6707,13 +6711,13 @@
       </c>
       <c r="B174" s="5" t="inlineStr">
         <is>
-          <t>BOLSA VACIO MPRO 20X30 100PZA</t>
+          <t>BAYETA MPRO ROLLO PUNTO AZUL 3KG</t>
         </is>
       </c>
       <c r="C174" s="11" t="n"/>
       <c r="D174" s="11" t="n"/>
       <c r="E174" s="11" t="n">
-        <v>11.95</v>
+        <v>18.47</v>
       </c>
       <c r="F174" s="11">
         <f>IF(D174&lt;&gt;"",D174,IF(C174&lt;&gt;"",C174,""))</f>
@@ -6745,13 +6749,13 @@
       </c>
       <c r="B175" s="5" t="inlineStr">
         <is>
-          <t>CALABACIN 2A MA 2KG</t>
+          <t>BOLSA VACIO MPRO 20X30 100PZA</t>
         </is>
       </c>
       <c r="C175" s="11" t="n"/>
       <c r="D175" s="11" t="n"/>
       <c r="E175" s="11" t="n">
-        <v>4.39</v>
+        <v>11.95</v>
       </c>
       <c r="F175" s="11">
         <f>IF(D175&lt;&gt;"",D175,IF(C175&lt;&gt;"",C175,""))</f>
@@ -6773,11 +6777,7 @@
         <f>IF(AND(C175&lt;&gt;"",D175&lt;&gt;""),IF(C175=0,"",D175/C175-1),"")</f>
         <v/>
       </c>
-      <c r="K175" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K175" s="5" t="n"/>
     </row>
     <row r="176">
       <c r="A176" s="5" t="inlineStr">
@@ -6787,13 +6787,13 @@
       </c>
       <c r="B176" s="5" t="inlineStr">
         <is>
-          <t>CALDO PESCADO KNORR 1KG</t>
+          <t>CALABACIN 2A MA 2KG</t>
         </is>
       </c>
       <c r="C176" s="11" t="n"/>
       <c r="D176" s="11" t="n"/>
       <c r="E176" s="11" t="n">
-        <v>10.35</v>
+        <v>4.39</v>
       </c>
       <c r="F176" s="11">
         <f>IF(D176&lt;&gt;"",D176,IF(C176&lt;&gt;"",C176,""))</f>
@@ -6815,7 +6815,11 @@
         <f>IF(AND(C176&lt;&gt;"",D176&lt;&gt;""),IF(C176=0,"",D176/C176-1),"")</f>
         <v/>
       </c>
-      <c r="K176" s="5" t="n"/>
+      <c r="K176" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="5" t="inlineStr">
@@ -6825,13 +6829,13 @@
       </c>
       <c r="B177" s="5" t="inlineStr">
         <is>
-          <t>CALDO POLLO KNORR 1KG</t>
+          <t>CALDO PESCADO KNORR 1KG</t>
         </is>
       </c>
       <c r="C177" s="11" t="n"/>
       <c r="D177" s="11" t="n"/>
       <c r="E177" s="11" t="n">
-        <v>8.5</v>
+        <v>10.35</v>
       </c>
       <c r="F177" s="11">
         <f>IF(D177&lt;&gt;"",D177,IF(C177&lt;&gt;"",C177,""))</f>
@@ -6853,11 +6857,7 @@
         <f>IF(AND(C177&lt;&gt;"",D177&lt;&gt;""),IF(C177=0,"",D177/C177-1),"")</f>
         <v/>
       </c>
-      <c r="K177" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K177" s="5" t="n"/>
     </row>
     <row r="178">
       <c r="A178" s="5" t="inlineStr">
@@ -6867,15 +6867,13 @@
       </c>
       <c r="B178" s="5" t="inlineStr">
         <is>
-          <t>CEBOLLA GUISOS MC SC 5KG</t>
-        </is>
-      </c>
-      <c r="C178" s="11" t="n">
-        <v>4.68</v>
-      </c>
+          <t>CALDO POLLO KNORR 1KG</t>
+        </is>
+      </c>
+      <c r="C178" s="11" t="n"/>
       <c r="D178" s="11" t="n"/>
       <c r="E178" s="11" t="n">
-        <v>5.67</v>
+        <v>8.5</v>
       </c>
       <c r="F178" s="11">
         <f>IF(D178&lt;&gt;"",D178,IF(C178&lt;&gt;"",C178,""))</f>
@@ -6899,7 +6897,7 @@
       </c>
       <c r="K178" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 4,13 / 4,72 / 4,83 / 5,67</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -6911,15 +6909,15 @@
       </c>
       <c r="B179" s="5" t="inlineStr">
         <is>
-          <t>CEBOLLETA BCA MJ</t>
+          <t>CEBOLLA GUISOS MC SC 5KG</t>
         </is>
       </c>
       <c r="C179" s="11" t="n">
-        <v>2.04</v>
+        <v>4.68</v>
       </c>
       <c r="D179" s="11" t="n"/>
       <c r="E179" s="11" t="n">
-        <v>2.04</v>
+        <v>5.67</v>
       </c>
       <c r="F179" s="11">
         <f>IF(D179&lt;&gt;"",D179,IF(C179&lt;&gt;"",C179,""))</f>
@@ -6943,7 +6941,7 @@
       </c>
       <c r="K179" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 4,13 / 4,72 / 4,83 / 5,67</t>
         </is>
       </c>
     </row>
@@ -6955,15 +6953,15 @@
       </c>
       <c r="B180" s="5" t="inlineStr">
         <is>
-          <t>CEBOLLETA CHINA MJ</t>
+          <t>CEBOLLETA BCA MJ</t>
         </is>
       </c>
       <c r="C180" s="11" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="D180" s="11" t="n"/>
       <c r="E180" s="11" t="n">
-        <v>1.49</v>
+        <v>2.04</v>
       </c>
       <c r="F180" s="11">
         <f>IF(D180&lt;&gt;"",D180,IF(C180&lt;&gt;"",C180,""))</f>
@@ -6999,15 +6997,15 @@
       </c>
       <c r="B181" s="5" t="inlineStr">
         <is>
-          <t>CEBOLLINO MC MJ 125G</t>
+          <t>CEBOLLETA CHINA MJ</t>
         </is>
       </c>
       <c r="C181" s="11" t="n">
-        <v>2.81</v>
+        <v>1.49</v>
       </c>
       <c r="D181" s="11" t="n"/>
       <c r="E181" s="11" t="n">
-        <v>3.73</v>
+        <v>1.49</v>
       </c>
       <c r="F181" s="11">
         <f>IF(D181&lt;&gt;"",D181,IF(C181&lt;&gt;"",C181,""))</f>
@@ -7031,7 +7029,7 @@
       </c>
       <c r="K181" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 2,81 / 3,62 / 3,73</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -7043,13 +7041,15 @@
       </c>
       <c r="B182" s="5" t="inlineStr">
         <is>
-          <t>CINTA LOMO ADB EXTRATIERNA EPZ</t>
-        </is>
-      </c>
-      <c r="C182" s="11" t="n"/>
+          <t>CEBOLLINO MC MJ 125G</t>
+        </is>
+      </c>
+      <c r="C182" s="11" t="n">
+        <v>2.81</v>
+      </c>
       <c r="D182" s="11" t="n"/>
       <c r="E182" s="11" t="n">
-        <v>7.02</v>
+        <v>3.73</v>
       </c>
       <c r="F182" s="11">
         <f>IF(D182&lt;&gt;"",D182,IF(C182&lt;&gt;"",C182,""))</f>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="K182" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 2,81 / 3,62 / 3,73</t>
         </is>
       </c>
     </row>
@@ -7085,13 +7085,13 @@
       </c>
       <c r="B183" s="5" t="inlineStr">
         <is>
-          <t>CORAZON LECHUGA ROMANA 2UD</t>
+          <t>CINTA LOMO ADB EXTRATIERNA EPZ</t>
         </is>
       </c>
       <c r="C183" s="11" t="n"/>
       <c r="D183" s="11" t="n"/>
       <c r="E183" s="11" t="n">
-        <v>1.97</v>
+        <v>7.02</v>
       </c>
       <c r="F183" s="11">
         <f>IF(D183&lt;&gt;"",D183,IF(C183&lt;&gt;"",C183,""))</f>
@@ -7127,13 +7127,13 @@
       </c>
       <c r="B184" s="5" t="inlineStr">
         <is>
-          <t>ENELDO MC BJ 125G</t>
+          <t>CORAZON LECHUGA ROMANA 2UD</t>
         </is>
       </c>
       <c r="C184" s="11" t="n"/>
       <c r="D184" s="11" t="n"/>
       <c r="E184" s="11" t="n">
-        <v>3.07</v>
+        <v>1.97</v>
       </c>
       <c r="F184" s="11">
         <f>IF(D184&lt;&gt;"",D184,IF(C184&lt;&gt;"",C184,""))</f>
@@ -7169,13 +7169,13 @@
       </c>
       <c r="B185" s="5" t="inlineStr">
         <is>
-          <t>ESTRAGON MC BJ 125G</t>
+          <t>ENELDO MC BJ 125G</t>
         </is>
       </c>
       <c r="C185" s="11" t="n"/>
       <c r="D185" s="11" t="n"/>
       <c r="E185" s="11" t="n">
-        <v>3.47</v>
+        <v>3.07</v>
       </c>
       <c r="F185" s="11">
         <f>IF(D185&lt;&gt;"",D185,IF(C185&lt;&gt;"",C185,""))</f>
@@ -7211,13 +7211,13 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>FOIE MICUIT ENTER MARTIKO 500G</t>
+          <t>ESTRAGON MC BJ 125G</t>
         </is>
       </c>
       <c r="C186" s="11" t="n"/>
       <c r="D186" s="11" t="n"/>
       <c r="E186" s="11" t="n">
-        <v>47.22</v>
+        <v>3.47</v>
       </c>
       <c r="F186" s="11">
         <f>IF(D186&lt;&gt;"",D186,IF(C186&lt;&gt;"",C186,""))</f>
@@ -7239,7 +7239,11 @@
         <f>IF(AND(C186&lt;&gt;"",D186&lt;&gt;""),IF(C186=0,"",D186/C186-1),"")</f>
         <v/>
       </c>
-      <c r="K186" s="5" t="n"/>
+      <c r="K186" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="5" t="inlineStr">
@@ -7249,13 +7253,13 @@
       </c>
       <c r="B187" s="5" t="inlineStr">
         <is>
-          <t>GUINDILLA 300G</t>
+          <t>FOIE MICUIT ENTER MARTIKO 500G</t>
         </is>
       </c>
       <c r="C187" s="11" t="n"/>
       <c r="D187" s="11" t="n"/>
       <c r="E187" s="11" t="n">
-        <v>11.76</v>
+        <v>47.22</v>
       </c>
       <c r="F187" s="11">
         <f>IF(D187&lt;&gt;"",D187,IF(C187&lt;&gt;"",C187,""))</f>
@@ -7277,11 +7281,7 @@
         <f>IF(AND(C187&lt;&gt;"",D187&lt;&gt;""),IF(C187=0,"",D187/C187-1),"")</f>
         <v/>
       </c>
-      <c r="K187" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K187" s="5" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="5" t="inlineStr">
@@ -7291,13 +7291,13 @@
       </c>
       <c r="B188" s="5" t="inlineStr">
         <is>
-          <t>HARINA TRIGO ESPECIAL FRITURA MC 1KG (PACK 10)</t>
+          <t>GUINDILLA 300G</t>
         </is>
       </c>
       <c r="C188" s="11" t="n"/>
       <c r="D188" s="11" t="n"/>
       <c r="E188" s="11" t="n">
-        <v>1.19</v>
+        <v>11.76</v>
       </c>
       <c r="F188" s="11">
         <f>IF(D188&lt;&gt;"",D188,IF(C188&lt;&gt;"",C188,""))</f>
@@ -7319,7 +7319,11 @@
         <f>IF(AND(C188&lt;&gt;"",D188&lt;&gt;""),IF(C188=0,"",D188/C188-1),"")</f>
         <v/>
       </c>
-      <c r="K188" s="5" t="n"/>
+      <c r="K188" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="5" t="inlineStr">
@@ -7329,13 +7333,13 @@
       </c>
       <c r="B189" s="5" t="inlineStr">
         <is>
-          <t>HIERBABUENA MC BJ 125G</t>
+          <t>HARINA TRIGO ESPECIAL FRITURA MC 1KG (PACK 10)</t>
         </is>
       </c>
       <c r="C189" s="11" t="n"/>
       <c r="D189" s="11" t="n"/>
       <c r="E189" s="11" t="n">
-        <v>3.07</v>
+        <v>1.19</v>
       </c>
       <c r="F189" s="11">
         <f>IF(D189&lt;&gt;"",D189,IF(C189&lt;&gt;"",C189,""))</f>
@@ -7357,11 +7361,7 @@
         <f>IF(AND(C189&lt;&gt;"",D189&lt;&gt;""),IF(C189=0,"",D189/C189-1),"")</f>
         <v/>
       </c>
-      <c r="K189" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K189" s="5" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="5" t="inlineStr">
@@ -7371,13 +7371,13 @@
       </c>
       <c r="B190" s="5" t="inlineStr">
         <is>
-          <t>HUEVO LIQUIDO MC BT 1L</t>
+          <t>HIERBABUENA MC BJ 125G</t>
         </is>
       </c>
       <c r="C190" s="11" t="n"/>
       <c r="D190" s="11" t="n"/>
       <c r="E190" s="11" t="n">
-        <v>5.14</v>
+        <v>3.07</v>
       </c>
       <c r="F190" s="11">
         <f>IF(D190&lt;&gt;"",D190,IF(C190&lt;&gt;"",C190,""))</f>
@@ -7399,7 +7399,11 @@
         <f>IF(AND(C190&lt;&gt;"",D190&lt;&gt;""),IF(C190=0,"",D190/C190-1),"")</f>
         <v/>
       </c>
-      <c r="K190" s="5" t="n"/>
+      <c r="K190" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="5" t="inlineStr">
@@ -7409,13 +7413,13 @@
       </c>
       <c r="B191" s="5" t="inlineStr">
         <is>
-          <t>KETCHUP ARO 1,85KG</t>
+          <t>HUEVO LIQUIDO MC BT 1L</t>
         </is>
       </c>
       <c r="C191" s="11" t="n"/>
       <c r="D191" s="11" t="n"/>
       <c r="E191" s="11" t="n">
-        <v>3.9</v>
+        <v>5.14</v>
       </c>
       <c r="F191" s="11">
         <f>IF(D191&lt;&gt;"",D191,IF(C191&lt;&gt;"",C191,""))</f>
@@ -7447,13 +7451,13 @@
       </c>
       <c r="B192" s="5" t="inlineStr">
         <is>
-          <t>LAUREL HOJA ARO 600G</t>
+          <t>KETCHUP ARO 1,85KG</t>
         </is>
       </c>
       <c r="C192" s="11" t="n"/>
       <c r="D192" s="11" t="n"/>
       <c r="E192" s="11" t="n">
-        <v>17.82</v>
+        <v>3.9</v>
       </c>
       <c r="F192" s="11">
         <f>IF(D192&lt;&gt;"",D192,IF(C192&lt;&gt;"",C192,""))</f>
@@ -7485,13 +7489,13 @@
       </c>
       <c r="B193" s="5" t="inlineStr">
         <is>
-          <t>LEA &amp; PERRINS SALSA WORCESTERSHIRE BIDON 2L</t>
+          <t>LAUREL HOJA ARO 600G</t>
         </is>
       </c>
       <c r="C193" s="11" t="n"/>
       <c r="D193" s="11" t="n"/>
       <c r="E193" s="11" t="n">
-        <v>20.44</v>
+        <v>17.82</v>
       </c>
       <c r="F193" s="11">
         <f>IF(D193&lt;&gt;"",D193,IF(C193&lt;&gt;"",C193,""))</f>
@@ -7523,13 +7527,13 @@
       </c>
       <c r="B194" s="5" t="inlineStr">
         <is>
-          <t>LECHE ENT ARO BK 1L (CAJA 6)</t>
+          <t>LEA &amp; PERRINS SALSA WORCESTERSHIRE BIDON 2L</t>
         </is>
       </c>
       <c r="C194" s="11" t="n"/>
       <c r="D194" s="11" t="n"/>
       <c r="E194" s="11" t="n">
-        <v>0.99</v>
+        <v>20.44</v>
       </c>
       <c r="F194" s="11">
         <f>IF(D194&lt;&gt;"",D194,IF(C194&lt;&gt;"",C194,""))</f>
@@ -7561,13 +7565,13 @@
       </c>
       <c r="B195" s="5" t="inlineStr">
         <is>
-          <t>LECHE FCA ENT PULEVA BT 1.5L</t>
+          <t>LECHE ENT ARO BK 1L (CAJA 6)</t>
         </is>
       </c>
       <c r="C195" s="11" t="n"/>
       <c r="D195" s="11" t="n"/>
       <c r="E195" s="11" t="n">
-        <v>2.94</v>
+        <v>0.99</v>
       </c>
       <c r="F195" s="11">
         <f>IF(D195&lt;&gt;"",D195,IF(C195&lt;&gt;"",C195,""))</f>
@@ -7599,13 +7603,13 @@
       </c>
       <c r="B196" s="5" t="inlineStr">
         <is>
-          <t>LIMAS CJ 4KG</t>
+          <t>LECHE FCA ENT PULEVA BT 1.5L</t>
         </is>
       </c>
       <c r="C196" s="11" t="n"/>
       <c r="D196" s="11" t="n"/>
       <c r="E196" s="11" t="n">
-        <v>12.97</v>
+        <v>2.94</v>
       </c>
       <c r="F196" s="11">
         <f>IF(D196&lt;&gt;"",D196,IF(C196&lt;&gt;"",C196,""))</f>
@@ -7627,11 +7631,7 @@
         <f>IF(AND(C196&lt;&gt;"",D196&lt;&gt;""),IF(C196=0,"",D196/C196-1),"")</f>
         <v/>
       </c>
-      <c r="K196" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K196" s="5" t="n"/>
     </row>
     <row r="197">
       <c r="A197" s="5" t="inlineStr">
@@ -7641,15 +7641,13 @@
       </c>
       <c r="B197" s="5" t="inlineStr">
         <is>
-          <t>LIMON 2A CJ 9KG</t>
-        </is>
-      </c>
-      <c r="C197" s="11" t="n">
-        <v>17.92</v>
-      </c>
+          <t>LIMAS CJ 4KG</t>
+        </is>
+      </c>
+      <c r="C197" s="11" t="n"/>
       <c r="D197" s="11" t="n"/>
       <c r="E197" s="11" t="n">
-        <v>15.24</v>
+        <v>12.97</v>
       </c>
       <c r="F197" s="11">
         <f>IF(D197&lt;&gt;"",D197,IF(C197&lt;&gt;"",C197,""))</f>
@@ -7673,7 +7671,7 @@
       </c>
       <c r="K197" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 12,31 / 12,97 / 13,41 / 13,70 / 15,24</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -7685,13 +7683,15 @@
       </c>
       <c r="B198" s="5" t="inlineStr">
         <is>
-          <t>LIMON MC C-3/4 CJ 6KG</t>
-        </is>
-      </c>
-      <c r="C198" s="11" t="n"/>
+          <t>LIMON 2A CJ 9KG</t>
+        </is>
+      </c>
+      <c r="C198" s="11" t="n">
+        <v>17.92</v>
+      </c>
       <c r="D198" s="11" t="n"/>
       <c r="E198" s="11" t="n">
-        <v>11.43</v>
+        <v>15.24</v>
       </c>
       <c r="F198" s="11">
         <f>IF(D198&lt;&gt;"",D198,IF(C198&lt;&gt;"",C198,""))</f>
@@ -7715,7 +7715,7 @@
       </c>
       <c r="K198" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 10,73 / 11,17 / 11,43</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 12,31 / 12,97 / 13,41 / 13,70 / 15,24</t>
         </is>
       </c>
     </row>
@@ -7727,15 +7727,13 @@
       </c>
       <c r="B199" s="5" t="inlineStr">
         <is>
-          <t>MANTEQUILLA PRESIDENT BQ 1KG</t>
-        </is>
-      </c>
-      <c r="C199" s="11" t="n">
-        <v>16.19</v>
-      </c>
+          <t>LIMON MC C-3/4 CJ 6KG</t>
+        </is>
+      </c>
+      <c r="C199" s="11" t="n"/>
       <c r="D199" s="11" t="n"/>
       <c r="E199" s="11" t="n">
-        <v>16.98</v>
+        <v>11.43</v>
       </c>
       <c r="F199" s="11">
         <f>IF(D199&lt;&gt;"",D199,IF(C199&lt;&gt;"",C199,""))</f>
@@ -7757,7 +7755,11 @@
         <f>IF(AND(C199&lt;&gt;"",D199&lt;&gt;""),IF(C199=0,"",D199/C199-1),"")</f>
         <v/>
       </c>
-      <c r="K199" s="5" t="n"/>
+      <c r="K199" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 10,73 / 11,17 / 11,43</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="5" t="inlineStr">
@@ -7767,13 +7769,15 @@
       </c>
       <c r="B200" s="5" t="inlineStr">
         <is>
-          <t>MANTEQUILLA PULEVA BQ 1KG</t>
-        </is>
-      </c>
-      <c r="C200" s="11" t="n"/>
+          <t>MANTEQUILLA PRESIDENT BQ 1KG</t>
+        </is>
+      </c>
+      <c r="C200" s="11" t="n">
+        <v>16.19</v>
+      </c>
       <c r="D200" s="11" t="n"/>
       <c r="E200" s="11" t="n">
-        <v>11.64</v>
+        <v>16.98</v>
       </c>
       <c r="F200" s="11">
         <f>IF(D200&lt;&gt;"",D200,IF(C200&lt;&gt;"",C200,""))</f>
@@ -7805,15 +7809,13 @@
       </c>
       <c r="B201" s="5" t="inlineStr">
         <is>
-          <t>NARANJA ZUMO MC SC 5KG</t>
-        </is>
-      </c>
-      <c r="C201" s="11" t="n">
-        <v>7.65</v>
-      </c>
+          <t>MANTEQUILLA PULEVA BQ 1KG</t>
+        </is>
+      </c>
+      <c r="C201" s="11" t="n"/>
       <c r="D201" s="11" t="n"/>
       <c r="E201" s="11" t="n">
-        <v>9.52</v>
+        <v>11.64</v>
       </c>
       <c r="F201" s="11">
         <f>IF(D201&lt;&gt;"",D201,IF(C201&lt;&gt;"",C201,""))</f>
@@ -7835,11 +7837,7 @@
         <f>IF(AND(C201&lt;&gt;"",D201&lt;&gt;""),IF(C201=0,"",D201/C201-1),"")</f>
         <v/>
       </c>
-      <c r="K201" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 7,55 / 8,13 / 9,52</t>
-        </is>
-      </c>
+      <c r="K201" s="5" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="5" t="inlineStr">
@@ -7849,13 +7847,15 @@
       </c>
       <c r="B202" s="5" t="inlineStr">
         <is>
-          <t>NATA MONTAR 35% +FIRMEZA 1L DEBIC</t>
-        </is>
-      </c>
-      <c r="C202" s="11" t="n"/>
+          <t>NARANJA ZUMO MC SC 5KG</t>
+        </is>
+      </c>
+      <c r="C202" s="11" t="n">
+        <v>7.65</v>
+      </c>
       <c r="D202" s="11" t="n"/>
       <c r="E202" s="11" t="n">
-        <v>7.07</v>
+        <v>9.52</v>
       </c>
       <c r="F202" s="11">
         <f>IF(D202&lt;&gt;"",D202,IF(C202&lt;&gt;"",C202,""))</f>
@@ -7877,7 +7877,11 @@
         <f>IF(AND(C202&lt;&gt;"",D202&lt;&gt;""),IF(C202=0,"",D202/C202-1),"")</f>
         <v/>
       </c>
-      <c r="K202" s="5" t="n"/>
+      <c r="K202" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 7,55 / 8,13 / 9,52</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="5" t="inlineStr">
@@ -7887,13 +7891,13 @@
       </c>
       <c r="B203" s="5" t="inlineStr">
         <is>
-          <t>PAN HOT DOG MC 12UD</t>
+          <t>NATA MONTAR 35% +FIRMEZA 1L DEBIC</t>
         </is>
       </c>
       <c r="C203" s="11" t="n"/>
       <c r="D203" s="11" t="n"/>
       <c r="E203" s="11" t="n">
-        <v>2.74</v>
+        <v>7.07</v>
       </c>
       <c r="F203" s="11">
         <f>IF(D203&lt;&gt;"",D203,IF(C203&lt;&gt;"",C203,""))</f>
@@ -7925,13 +7929,13 @@
       </c>
       <c r="B204" s="5" t="inlineStr">
         <is>
-          <t>PANGA FTE 120/170 ARO 800G</t>
+          <t>PAN HOT DOG MC 12UD</t>
         </is>
       </c>
       <c r="C204" s="11" t="n"/>
       <c r="D204" s="11" t="n"/>
       <c r="E204" s="11" t="n">
-        <v>5.22</v>
+        <v>2.74</v>
       </c>
       <c r="F204" s="11">
         <f>IF(D204&lt;&gt;"",D204,IF(C204&lt;&gt;"",C204,""))</f>
@@ -7963,14 +7967,14 @@
       </c>
       <c r="B205" s="5" t="inlineStr">
         <is>
-          <t>PATATA LAV AGRIA MC C60/80 12KG</t>
-        </is>
-      </c>
-      <c r="C205" s="11" t="n">
-        <v>11.5</v>
-      </c>
+          <t>PANGA FTE 120/170 ARO 800G</t>
+        </is>
+      </c>
+      <c r="C205" s="11" t="n"/>
       <c r="D205" s="11" t="n"/>
-      <c r="E205" s="11" t="n"/>
+      <c r="E205" s="11" t="n">
+        <v>5.22</v>
+      </c>
       <c r="F205" s="11">
         <f>IF(D205&lt;&gt;"",D205,IF(C205&lt;&gt;"",C205,""))</f>
         <v/>
@@ -8001,14 +8005,14 @@
       </c>
       <c r="B206" s="5" t="inlineStr">
         <is>
-          <t>PEREJIL GRANEL 800G</t>
-        </is>
-      </c>
-      <c r="C206" s="11" t="n"/>
+          <t>PATATA LAV AGRIA MC C60/80 12KG</t>
+        </is>
+      </c>
+      <c r="C206" s="11" t="n">
+        <v>11.5</v>
+      </c>
       <c r="D206" s="11" t="n"/>
-      <c r="E206" s="11" t="n">
-        <v>1.71</v>
-      </c>
+      <c r="E206" s="11" t="n"/>
       <c r="F206" s="11">
         <f>IF(D206&lt;&gt;"",D206,IF(C206&lt;&gt;"",C206,""))</f>
         <v/>
@@ -8029,11 +8033,7 @@
         <f>IF(AND(C206&lt;&gt;"",D206&lt;&gt;""),IF(C206=0,"",D206/C206-1),"")</f>
         <v/>
       </c>
-      <c r="K206" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K206" s="5" t="n"/>
     </row>
     <row r="207">
       <c r="A207" s="5" t="inlineStr">
@@ -8043,13 +8043,13 @@
       </c>
       <c r="B207" s="5" t="inlineStr">
         <is>
-          <t>PIMENTON DULCE DOP DALIA 800G</t>
+          <t>PEREJIL GRANEL 800G</t>
         </is>
       </c>
       <c r="C207" s="11" t="n"/>
       <c r="D207" s="11" t="n"/>
       <c r="E207" s="11" t="n">
-        <v>14.7</v>
+        <v>1.71</v>
       </c>
       <c r="F207" s="11">
         <f>IF(D207&lt;&gt;"",D207,IF(C207&lt;&gt;"",C207,""))</f>
@@ -8071,7 +8071,11 @@
         <f>IF(AND(C207&lt;&gt;"",D207&lt;&gt;""),IF(C207=0,"",D207/C207-1),"")</f>
         <v/>
       </c>
-      <c r="K207" s="5" t="n"/>
+      <c r="K207" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="5" t="inlineStr">
@@ -8081,7 +8085,7 @@
       </c>
       <c r="B208" s="5" t="inlineStr">
         <is>
-          <t>PIMENTON PICANTE DOP DALIA 800G</t>
+          <t>PIMENTON DULCE DOP DALIA 800G</t>
         </is>
       </c>
       <c r="C208" s="11" t="n"/>
@@ -8119,13 +8123,13 @@
       </c>
       <c r="B209" s="5" t="inlineStr">
         <is>
-          <t>PIMIENTO LAMYO RJ ARO CJ 4,5/5KG</t>
+          <t>PIMENTON PICANTE DOP DALIA 800G</t>
         </is>
       </c>
       <c r="C209" s="11" t="n"/>
       <c r="D209" s="11" t="n"/>
       <c r="E209" s="11" t="n">
-        <v>13.3</v>
+        <v>14.7</v>
       </c>
       <c r="F209" s="11">
         <f>IF(D209&lt;&gt;"",D209,IF(C209&lt;&gt;"",C209,""))</f>
@@ -8147,11 +8151,7 @@
         <f>IF(AND(C209&lt;&gt;"",D209&lt;&gt;""),IF(C209=0,"",D209/C209-1),"")</f>
         <v/>
       </c>
-      <c r="K209" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 11,54 / 12,75 / 12,86 / 13,30</t>
-        </is>
-      </c>
+      <c r="K209" s="5" t="n"/>
     </row>
     <row r="210">
       <c r="A210" s="5" t="inlineStr">
@@ -8161,15 +8161,13 @@
       </c>
       <c r="B210" s="5" t="inlineStr">
         <is>
-          <t>PIMIENTO LAMYO VDE ARO CJ 4,5/5KG</t>
-        </is>
-      </c>
-      <c r="C210" s="11" t="n">
-        <v>10.62</v>
-      </c>
+          <t>PIMIENTO LAMYO RJ ARO CJ 4,5/5KG</t>
+        </is>
+      </c>
+      <c r="C210" s="11" t="n"/>
       <c r="D210" s="11" t="n"/>
       <c r="E210" s="11" t="n">
-        <v>14.73</v>
+        <v>13.3</v>
       </c>
       <c r="F210" s="11">
         <f>IF(D210&lt;&gt;"",D210,IF(C210&lt;&gt;"",C210,""))</f>
@@ -8193,7 +8191,7 @@
       </c>
       <c r="K210" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 10,07 / 10,33 / 14,29 / 14,73</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 11,54 / 12,75 / 12,86 / 13,30</t>
         </is>
       </c>
     </row>
@@ -8205,13 +8203,15 @@
       </c>
       <c r="B211" s="5" t="inlineStr">
         <is>
-          <t>POLLO PECHUGA VC MC</t>
-        </is>
-      </c>
-      <c r="C211" s="11" t="n"/>
+          <t>PIMIENTO LAMYO VDE ARO CJ 4,5/5KG</t>
+        </is>
+      </c>
+      <c r="C211" s="11" t="n">
+        <v>10.62</v>
+      </c>
       <c r="D211" s="11" t="n"/>
       <c r="E211" s="11" t="n">
-        <v>5.93</v>
+        <v>14.73</v>
       </c>
       <c r="F211" s="11">
         <f>IF(D211&lt;&gt;"",D211,IF(C211&lt;&gt;"",C211,""))</f>
@@ -8235,7 +8235,7 @@
       </c>
       <c r="K211" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 10,07 / 10,33 / 14,29 / 14,73</t>
         </is>
       </c>
     </row>
@@ -8247,13 +8247,13 @@
       </c>
       <c r="B212" s="5" t="inlineStr">
         <is>
-          <t>POLLO TRASERO VC</t>
+          <t>POLLO PECHUGA VC MC</t>
         </is>
       </c>
       <c r="C212" s="11" t="n"/>
       <c r="D212" s="11" t="n"/>
       <c r="E212" s="11" t="n">
-        <v>2.6</v>
+        <v>5.93</v>
       </c>
       <c r="F212" s="11">
         <f>IF(D212&lt;&gt;"",D212,IF(C212&lt;&gt;"",C212,""))</f>
@@ -8289,13 +8289,13 @@
       </c>
       <c r="B213" s="5" t="inlineStr">
         <is>
-          <t>PULCO BT 70CL LIMON</t>
+          <t>POLLO TRASERO VC</t>
         </is>
       </c>
       <c r="C213" s="11" t="n"/>
       <c r="D213" s="11" t="n"/>
       <c r="E213" s="11" t="n">
-        <v>4.07</v>
+        <v>2.6</v>
       </c>
       <c r="F213" s="11">
         <f>IF(D213&lt;&gt;"",D213,IF(C213&lt;&gt;"",C213,""))</f>
@@ -8331,13 +8331,13 @@
       </c>
       <c r="B214" s="5" t="inlineStr">
         <is>
-          <t>QUESO RALLADO 4 QUESOS MC 1KG</t>
+          <t>PULCO BT 70CL LIMON</t>
         </is>
       </c>
       <c r="C214" s="11" t="n"/>
       <c r="D214" s="11" t="n"/>
       <c r="E214" s="11" t="n">
-        <v>9.66</v>
+        <v>4.07</v>
       </c>
       <c r="F214" s="11">
         <f>IF(D214&lt;&gt;"",D214,IF(C214&lt;&gt;"",C214,""))</f>
@@ -8359,7 +8359,11 @@
         <f>IF(AND(C214&lt;&gt;"",D214&lt;&gt;""),IF(C214=0,"",D214/C214-1),"")</f>
         <v/>
       </c>
-      <c r="K214" s="5" t="n"/>
+      <c r="K214" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="5" t="inlineStr">
@@ -8369,13 +8373,13 @@
       </c>
       <c r="B215" s="5" t="inlineStr">
         <is>
-          <t>ROMERO MC BJ 125G</t>
+          <t>QUESO RALLADO 4 QUESOS MC 1KG</t>
         </is>
       </c>
       <c r="C215" s="11" t="n"/>
       <c r="D215" s="11" t="n"/>
       <c r="E215" s="11" t="n">
-        <v>3.19</v>
+        <v>9.66</v>
       </c>
       <c r="F215" s="11">
         <f>IF(D215&lt;&gt;"",D215,IF(C215&lt;&gt;"",C215,""))</f>
@@ -8397,11 +8401,7 @@
         <f>IF(AND(C215&lt;&gt;"",D215&lt;&gt;""),IF(C215=0,"",D215/C215-1),"")</f>
         <v/>
       </c>
-      <c r="K215" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K215" s="5" t="n"/>
     </row>
     <row r="216">
       <c r="A216" s="5" t="inlineStr">
@@ -8411,13 +8411,13 @@
       </c>
       <c r="B216" s="5" t="inlineStr">
         <is>
-          <t>ROTULADOR PERM ARO NEGRO (CAJA 12)</t>
+          <t>ROMERO MC BJ 125G</t>
         </is>
       </c>
       <c r="C216" s="11" t="n"/>
       <c r="D216" s="11" t="n"/>
       <c r="E216" s="11" t="n">
-        <v>13.27</v>
+        <v>3.19</v>
       </c>
       <c r="F216" s="11">
         <f>IF(D216&lt;&gt;"",D216,IF(C216&lt;&gt;"",C216,""))</f>
@@ -8439,7 +8439,11 @@
         <f>IF(AND(C216&lt;&gt;"",D216&lt;&gt;""),IF(C216=0,"",D216/C216-1),"")</f>
         <v/>
       </c>
-      <c r="K216" s="5" t="n"/>
+      <c r="K216" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="5" t="inlineStr">
@@ -8449,13 +8453,13 @@
       </c>
       <c r="B217" s="5" t="inlineStr">
         <is>
-          <t>SAL FINA MC 1KG (PACK 12)</t>
+          <t>ROTULADOR PERM ARO NEGRO (CAJA 12)</t>
         </is>
       </c>
       <c r="C217" s="11" t="n"/>
       <c r="D217" s="11" t="n"/>
       <c r="E217" s="11" t="n">
-        <v>0.42</v>
+        <v>13.27</v>
       </c>
       <c r="F217" s="11">
         <f>IF(D217&lt;&gt;"",D217,IF(C217&lt;&gt;"",C217,""))</f>
@@ -8487,7 +8491,7 @@
       </c>
       <c r="B218" s="5" t="inlineStr">
         <is>
-          <t>SAL GRUESA SECA MC 1KG (PACK 12)</t>
+          <t>SAL FINA MC 1KG (PACK 12)</t>
         </is>
       </c>
       <c r="C218" s="11" t="n"/>
@@ -8525,15 +8529,13 @@
       </c>
       <c r="B219" s="5" t="inlineStr">
         <is>
-          <t>SAL MALDON 1.4 KG</t>
-        </is>
-      </c>
-      <c r="C219" s="11" t="n">
-        <v>23.64</v>
-      </c>
+          <t>SAL GRUESA SECA MC 1KG (PACK 12)</t>
+        </is>
+      </c>
+      <c r="C219" s="11" t="n"/>
       <c r="D219" s="11" t="n"/>
       <c r="E219" s="11" t="n">
-        <v>23.64</v>
+        <v>0.42</v>
       </c>
       <c r="F219" s="11">
         <f>IF(D219&lt;&gt;"",D219,IF(C219&lt;&gt;"",C219,""))</f>
@@ -8555,11 +8557,7 @@
         <f>IF(AND(C219&lt;&gt;"",D219&lt;&gt;""),IF(C219=0,"",D219/C219-1),"")</f>
         <v/>
       </c>
-      <c r="K219" s="5" t="inlineStr">
-        <is>
-          <t>Varios precios en septiembre: 22,19 / 23,64</t>
-        </is>
-      </c>
+      <c r="K219" s="5" t="n"/>
     </row>
     <row r="220">
       <c r="A220" s="5" t="inlineStr">
@@ -8569,13 +8567,15 @@
       </c>
       <c r="B220" s="5" t="inlineStr">
         <is>
-          <t>SALCHICHA FRANK. HTDOG 1KG ARO</t>
-        </is>
-      </c>
-      <c r="C220" s="11" t="n"/>
+          <t>SAL MALDON 1.4 KG</t>
+        </is>
+      </c>
+      <c r="C220" s="11" t="n">
+        <v>23.64</v>
+      </c>
       <c r="D220" s="11" t="n"/>
       <c r="E220" s="11" t="n">
-        <v>3.39</v>
+        <v>23.64</v>
       </c>
       <c r="F220" s="11">
         <f>IF(D220&lt;&gt;"",D220,IF(C220&lt;&gt;"",C220,""))</f>
@@ -8597,7 +8597,11 @@
         <f>IF(AND(C220&lt;&gt;"",D220&lt;&gt;""),IF(C220=0,"",D220/C220-1),"")</f>
         <v/>
       </c>
-      <c r="K220" s="5" t="n"/>
+      <c r="K220" s="5" t="inlineStr">
+        <is>
+          <t>Varios precios en septiembre: 22,19 / 23,64</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="5" t="inlineStr">
@@ -8607,13 +8611,13 @@
       </c>
       <c r="B221" s="5" t="inlineStr">
         <is>
-          <t>SOLOMILLO CERDO C/C CNG 5KG</t>
+          <t>SALCHICHA FRANK. HTDOG 1KG ARO</t>
         </is>
       </c>
       <c r="C221" s="11" t="n"/>
       <c r="D221" s="11" t="n"/>
       <c r="E221" s="11" t="n">
-        <v>29.1</v>
+        <v>3.39</v>
       </c>
       <c r="F221" s="11">
         <f>IF(D221&lt;&gt;"",D221,IF(C221&lt;&gt;"",C221,""))</f>
@@ -8635,11 +8639,7 @@
         <f>IF(AND(C221&lt;&gt;"",D221&lt;&gt;""),IF(C221=0,"",D221/C221-1),"")</f>
         <v/>
       </c>
-      <c r="K221" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K221" s="5" t="n"/>
     </row>
     <row r="222">
       <c r="A222" s="5" t="inlineStr">
@@ -8649,13 +8649,13 @@
       </c>
       <c r="B222" s="5" t="inlineStr">
         <is>
-          <t>SPAGHETTI ARO 5KG</t>
+          <t>SOLOMILLO CERDO C/C CNG 5KG</t>
         </is>
       </c>
       <c r="C222" s="11" t="n"/>
       <c r="D222" s="11" t="n"/>
       <c r="E222" s="11" t="n">
-        <v>6.45</v>
+        <v>29.1</v>
       </c>
       <c r="F222" s="11">
         <f>IF(D222&lt;&gt;"",D222,IF(C222&lt;&gt;"",C222,""))</f>
@@ -8677,7 +8677,11 @@
         <f>IF(AND(C222&lt;&gt;"",D222&lt;&gt;""),IF(C222=0,"",D222/C222-1),"")</f>
         <v/>
       </c>
-      <c r="K222" s="5" t="n"/>
+      <c r="K222" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="5" t="inlineStr">
@@ -8687,13 +8691,13 @@
       </c>
       <c r="B223" s="5" t="inlineStr">
         <is>
-          <t>SSA BBQ MC 1,85KG</t>
+          <t>SPAGHETTI ARO 5KG</t>
         </is>
       </c>
       <c r="C223" s="11" t="n"/>
       <c r="D223" s="11" t="n"/>
       <c r="E223" s="11" t="n">
-        <v>5.77</v>
+        <v>6.45</v>
       </c>
       <c r="F223" s="11">
         <f>IF(D223&lt;&gt;"",D223,IF(C223&lt;&gt;"",C223,""))</f>
@@ -8725,13 +8729,13 @@
       </c>
       <c r="B224" s="5" t="inlineStr">
         <is>
-          <t>SSA KIMCHI MOMOYA 1,2KG</t>
+          <t>SSA BBQ MC 1,85KG</t>
         </is>
       </c>
       <c r="C224" s="11" t="n"/>
       <c r="D224" s="11" t="n"/>
       <c r="E224" s="11" t="n">
-        <v>16.85</v>
+        <v>5.77</v>
       </c>
       <c r="F224" s="11">
         <f>IF(D224&lt;&gt;"",D224,IF(C224&lt;&gt;"",C224,""))</f>
@@ -8763,15 +8767,13 @@
       </c>
       <c r="B225" s="5" t="inlineStr">
         <is>
-          <t>SSA SOJA KIKKOMAN 1L</t>
-        </is>
-      </c>
-      <c r="C225" s="11" t="n">
-        <v>9.029999999999999</v>
-      </c>
+          <t>SSA KIMCHI MOMOYA 1,2KG</t>
+        </is>
+      </c>
+      <c r="C225" s="11" t="n"/>
       <c r="D225" s="11" t="n"/>
       <c r="E225" s="11" t="n">
-        <v>9.029999999999999</v>
+        <v>16.85</v>
       </c>
       <c r="F225" s="11">
         <f>IF(D225&lt;&gt;"",D225,IF(C225&lt;&gt;"",C225,""))</f>
@@ -8803,13 +8805,15 @@
       </c>
       <c r="B226" s="5" t="inlineStr">
         <is>
-          <t>TABASCO SALSA PICANTE 60ML (PACK 6)</t>
-        </is>
-      </c>
-      <c r="C226" s="11" t="n"/>
+          <t>SSA SOJA KIKKOMAN 1L</t>
+        </is>
+      </c>
+      <c r="C226" s="11" t="n">
+        <v>9.029999999999999</v>
+      </c>
       <c r="D226" s="11" t="n"/>
       <c r="E226" s="11" t="n">
-        <v>19.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F226" s="11">
         <f>IF(D226&lt;&gt;"",D226,IF(C226&lt;&gt;"",C226,""))</f>
@@ -8841,13 +8845,13 @@
       </c>
       <c r="B227" s="5" t="inlineStr">
         <is>
-          <t>TOMATE C-GG MAD2/3 BJ</t>
+          <t>TABASCO SALSA PICANTE 60ML (PACK 6)</t>
         </is>
       </c>
       <c r="C227" s="11" t="n"/>
       <c r="D227" s="11" t="n"/>
       <c r="E227" s="11" t="n">
-        <v>6.59</v>
+        <v>19.99</v>
       </c>
       <c r="F227" s="11">
         <f>IF(D227&lt;&gt;"",D227,IF(C227&lt;&gt;"",C227,""))</f>
@@ -8869,11 +8873,7 @@
         <f>IF(AND(C227&lt;&gt;"",D227&lt;&gt;""),IF(C227=0,"",D227/C227-1),"")</f>
         <v/>
       </c>
-      <c r="K227" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 3,51 / 5,12 / 6,59</t>
-        </is>
-      </c>
+      <c r="K227" s="5" t="n"/>
     </row>
     <row r="228">
       <c r="A228" s="5" t="inlineStr">
@@ -8883,13 +8883,13 @@
       </c>
       <c r="B228" s="5" t="inlineStr">
         <is>
-          <t>TOMATE DOBLE CONC MUTTI LT880G</t>
+          <t>TOMATE C-GG MAD2/3 BJ</t>
         </is>
       </c>
       <c r="C228" s="11" t="n"/>
       <c r="D228" s="11" t="n"/>
       <c r="E228" s="11" t="n">
-        <v>7.15</v>
+        <v>6.59</v>
       </c>
       <c r="F228" s="11">
         <f>IF(D228&lt;&gt;"",D228,IF(C228&lt;&gt;"",C228,""))</f>
@@ -8911,7 +8911,11 @@
         <f>IF(AND(C228&lt;&gt;"",D228&lt;&gt;""),IF(C228=0,"",D228/C228-1),"")</f>
         <v/>
       </c>
-      <c r="K228" s="5" t="n"/>
+      <c r="K228" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 3,51 / 5,12 / 6,59</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="5" t="inlineStr">
@@ -8921,13 +8925,13 @@
       </c>
       <c r="B229" s="5" t="inlineStr">
         <is>
-          <t>TOMILLO MC BJ 125G</t>
+          <t>TOMATE DOBLE CONC MUTTI LT880G</t>
         </is>
       </c>
       <c r="C229" s="11" t="n"/>
       <c r="D229" s="11" t="n"/>
       <c r="E229" s="11" t="n">
-        <v>3.18</v>
+        <v>7.15</v>
       </c>
       <c r="F229" s="11">
         <f>IF(D229&lt;&gt;"",D229,IF(C229&lt;&gt;"",C229,""))</f>
@@ -8949,11 +8953,7 @@
         <f>IF(AND(C229&lt;&gt;"",D229&lt;&gt;""),IF(C229=0,"",D229/C229-1),"")</f>
         <v/>
       </c>
-      <c r="K229" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
-        </is>
-      </c>
+      <c r="K229" s="5" t="n"/>
     </row>
     <row r="230">
       <c r="A230" s="5" t="inlineStr">
@@ -8963,13 +8963,13 @@
       </c>
       <c r="B230" s="5" t="inlineStr">
         <is>
-          <t>VINAGRE VINO BCO MC 5L</t>
+          <t>TOMILLO MC BJ 125G</t>
         </is>
       </c>
       <c r="C230" s="11" t="n"/>
       <c r="D230" s="11" t="n"/>
       <c r="E230" s="11" t="n">
-        <v>3.91</v>
+        <v>3.18</v>
       </c>
       <c r="F230" s="11">
         <f>IF(D230&lt;&gt;"",D230,IF(C230&lt;&gt;"",C230,""))</f>
@@ -8991,7 +8991,11 @@
         <f>IF(AND(C230&lt;&gt;"",D230&lt;&gt;""),IF(C230=0,"",D230/C230-1),"")</f>
         <v/>
       </c>
-      <c r="K230" s="5" t="n"/>
+      <c r="K230" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="5" t="inlineStr">
@@ -9001,13 +9005,13 @@
       </c>
       <c r="B231" s="5" t="inlineStr">
         <is>
-          <t>VINO BCO CERRO CRUZ BRIK 1L (CAJA 12)</t>
+          <t>VINAGRE VINO BCO MC 5L</t>
         </is>
       </c>
       <c r="C231" s="11" t="n"/>
       <c r="D231" s="11" t="n"/>
       <c r="E231" s="11" t="n">
-        <v>1.15</v>
+        <v>3.91</v>
       </c>
       <c r="F231" s="11">
         <f>IF(D231&lt;&gt;"",D231,IF(C231&lt;&gt;"",C231,""))</f>
@@ -9039,15 +9043,13 @@
       </c>
       <c r="B232" s="5" t="inlineStr">
         <is>
-          <t>ZANAHORIA MC 5KG</t>
-        </is>
-      </c>
-      <c r="C232" s="11" t="n">
-        <v>6.11</v>
-      </c>
+          <t>VINO BCO CERRO CRUZ BRIK 1L (CAJA 12)</t>
+        </is>
+      </c>
+      <c r="C232" s="11" t="n"/>
       <c r="D232" s="11" t="n"/>
       <c r="E232" s="11" t="n">
-        <v>5.82</v>
+        <v>1.15</v>
       </c>
       <c r="F232" s="11">
         <f>IF(D232&lt;&gt;"",D232,IF(C232&lt;&gt;"",C232,""))</f>
@@ -9069,31 +9071,25 @@
         <f>IF(AND(C232&lt;&gt;"",D232&lt;&gt;""),IF(C232=0,"",D232/C232-1),"")</f>
         <v/>
       </c>
-      <c r="K232" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 5,25 / 5,49 / 5,82</t>
-        </is>
-      </c>
+      <c r="K232" s="5" t="n"/>
     </row>
     <row r="233">
       <c r="A233" s="5" t="inlineStr">
         <is>
-          <t>MANUEL AMBRES</t>
+          <t>MAKRO</t>
         </is>
       </c>
       <c r="B233" s="5" t="inlineStr">
         <is>
-          <t>RACION CECINA PREMIUM 100GR (BLACK ANGUS)</t>
+          <t>ZANAHORIA MC 5KG</t>
         </is>
       </c>
       <c r="C233" s="11" t="n">
-        <v>7.35</v>
-      </c>
-      <c r="D233" s="11" t="n">
-        <v>7.35</v>
-      </c>
+        <v>6.11</v>
+      </c>
+      <c r="D233" s="11" t="n"/>
       <c r="E233" s="11" t="n">
-        <v>7.35</v>
+        <v>5.82</v>
       </c>
       <c r="F233" s="11">
         <f>IF(D233&lt;&gt;"",D233,IF(C233&lt;&gt;"",C233,""))</f>
@@ -9115,7 +9111,11 @@
         <f>IF(AND(C233&lt;&gt;"",D233&lt;&gt;""),IF(C233=0,"",D233/C233-1),"")</f>
         <v/>
       </c>
-      <c r="K233" s="5" t="n"/>
+      <c r="K233" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en septiembre: 5,25 / 5,49 / 5,82</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="5" t="inlineStr">
@@ -9125,15 +9125,17 @@
       </c>
       <c r="B234" s="5" t="inlineStr">
         <is>
-          <t>RACION CECINA PREMIUM 100GR WAGYU</t>
+          <t>RACION CECINA PREMIUM 100GR (BLACK ANGUS)</t>
         </is>
       </c>
       <c r="C234" s="11" t="n">
-        <v>16</v>
-      </c>
-      <c r="D234" s="11" t="n"/>
+        <v>7.35</v>
+      </c>
+      <c r="D234" s="11" t="n">
+        <v>7.35</v>
+      </c>
       <c r="E234" s="11" t="n">
-        <v>16</v>
+        <v>7.35</v>
       </c>
       <c r="F234" s="11">
         <f>IF(D234&lt;&gt;"",D234,IF(C234&lt;&gt;"",C234,""))</f>
@@ -9155,11 +9157,7 @@
         <f>IF(AND(C234&lt;&gt;"",D234&lt;&gt;""),IF(C234=0,"",D234/C234-1),"")</f>
         <v/>
       </c>
-      <c r="K234" s="5" t="inlineStr">
-        <is>
-          <t>En julio figuraba como «cecina black angus wagyu»</t>
-        </is>
-      </c>
+      <c r="K234" s="5" t="n"/>
     </row>
     <row r="235">
       <c r="A235" s="5" t="inlineStr">
@@ -9169,17 +9167,15 @@
       </c>
       <c r="B235" s="5" t="inlineStr">
         <is>
-          <t>RACION J. BELLOTA 100% 100GR</t>
+          <t>RACION CECINA PREMIUM 100GR WAGYU</t>
         </is>
       </c>
       <c r="C235" s="11" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="D235" s="11" t="n">
-        <v>13.9</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="D235" s="11" t="n"/>
       <c r="E235" s="11" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="F235" s="11">
         <f>IF(D235&lt;&gt;"",D235,IF(C235&lt;&gt;"",C235,""))</f>
@@ -9201,27 +9197,31 @@
         <f>IF(AND(C235&lt;&gt;"",D235&lt;&gt;""),IF(C235=0,"",D235/C235-1),"")</f>
         <v/>
       </c>
-      <c r="K235" s="5" t="n"/>
+      <c r="K235" s="5" t="inlineStr">
+        <is>
+          <t>En julio figuraba como «cecina black angus wagyu»</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="5" t="inlineStr">
         <is>
-          <t>MARTIN CANEDA</t>
+          <t>MANUEL AMBRES</t>
         </is>
       </c>
       <c r="B236" s="5" t="inlineStr">
         <is>
-          <t>BERBERECHO</t>
+          <t>RACION J. BELLOTA 100% 100GR</t>
         </is>
       </c>
       <c r="C236" s="11" t="n">
-        <v>25</v>
+        <v>13.9</v>
       </c>
       <c r="D236" s="11" t="n">
-        <v>24</v>
+        <v>13.9</v>
       </c>
       <c r="E236" s="11" t="n">
-        <v>22</v>
+        <v>13.9</v>
       </c>
       <c r="F236" s="11">
         <f>IF(D236&lt;&gt;"",D236,IF(C236&lt;&gt;"",C236,""))</f>
@@ -9243,11 +9243,7 @@
         <f>IF(AND(C236&lt;&gt;"",D236&lt;&gt;""),IF(C236=0,"",D236/C236-1),"")</f>
         <v/>
       </c>
-      <c r="K236" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 24,00 / 25,00. Varios precios en agosto: 22,00 / 24,00</t>
-        </is>
-      </c>
+      <c r="K236" s="5" t="n"/>
     </row>
     <row r="237">
       <c r="A237" s="5" t="inlineStr">
@@ -9257,17 +9253,17 @@
       </c>
       <c r="B237" s="5" t="inlineStr">
         <is>
-          <t>CAMARON</t>
+          <t>BERBERECHO</t>
         </is>
       </c>
       <c r="C237" s="11" t="n">
-        <v>98</v>
+        <v>25</v>
       </c>
       <c r="D237" s="11" t="n">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="E237" s="11" t="n">
-        <v>98</v>
+        <v>22</v>
       </c>
       <c r="F237" s="11">
         <f>IF(D237&lt;&gt;"",D237,IF(C237&lt;&gt;"",C237,""))</f>
@@ -9291,7 +9287,7 @@
       </c>
       <c r="K237" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 95,00 / 96,00 / 98,00. Varios precios en septiembre: 97,00 / 98,00</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 24,00 / 25,00. Varios precios en agosto: 22,00 / 24,00</t>
         </is>
       </c>
     </row>
@@ -9303,17 +9299,17 @@
       </c>
       <c r="B238" s="5" t="inlineStr">
         <is>
-          <t>CHOCHAS GDA</t>
+          <t>CAMARON</t>
         </is>
       </c>
       <c r="C238" s="11" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="D238" s="11" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="E238" s="11" t="n">
-        <v>50</v>
+        <v>98</v>
       </c>
       <c r="F238" s="11">
         <f>IF(D238&lt;&gt;"",D238,IF(C238&lt;&gt;"",C238,""))</f>
@@ -9337,7 +9333,7 @@
       </c>
       <c r="K238" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 95,00 / 96,00 / 98,00. Varios precios en septiembre: 97,00 / 98,00</t>
         </is>
       </c>
     </row>
@@ -9349,7 +9345,7 @@
       </c>
       <c r="B239" s="5" t="inlineStr">
         <is>
-          <t>CHOCHAS TDA</t>
+          <t>CHOCHAS GDA</t>
         </is>
       </c>
       <c r="C239" s="11" t="n">
@@ -9395,17 +9391,17 @@
       </c>
       <c r="B240" s="5" t="inlineStr">
         <is>
-          <t>MEJILLONES</t>
+          <t>CHOCHAS TDA</t>
         </is>
       </c>
       <c r="C240" s="11" t="n">
-        <v>2.7</v>
+        <v>50</v>
       </c>
       <c r="D240" s="11" t="n">
-        <v>2.7</v>
+        <v>50</v>
       </c>
       <c r="E240" s="11" t="n">
-        <v>2.7</v>
+        <v>50</v>
       </c>
       <c r="F240" s="11">
         <f>IF(D240&lt;&gt;"",D240,IF(C240&lt;&gt;"",C240,""))</f>
@@ -9441,17 +9437,17 @@
       </c>
       <c r="B241" s="5" t="inlineStr">
         <is>
-          <t>PERCEBES GDO</t>
+          <t>MEJILLONES</t>
         </is>
       </c>
       <c r="C241" s="11" t="n">
-        <v>95</v>
+        <v>2.7</v>
       </c>
       <c r="D241" s="11" t="n">
-        <v>95</v>
+        <v>2.7</v>
       </c>
       <c r="E241" s="11" t="n">
-        <v>95</v>
+        <v>2.7</v>
       </c>
       <c r="F241" s="11">
         <f>IF(D241&lt;&gt;"",D241,IF(C241&lt;&gt;"",C241,""))</f>
@@ -9482,18 +9478,22 @@
     <row r="242">
       <c r="A242" s="5" t="inlineStr">
         <is>
-          <t>MAXXIMO (MOLLETES)</t>
+          <t>MARTIN CANEDA</t>
         </is>
       </c>
       <c r="B242" s="5" t="inlineStr">
         <is>
-          <t>MOLLETES (UD)</t>
-        </is>
-      </c>
-      <c r="C242" s="11" t="n"/>
-      <c r="D242" s="11" t="n"/>
+          <t>PERCEBES GDO</t>
+        </is>
+      </c>
+      <c r="C242" s="11" t="n">
+        <v>95</v>
+      </c>
+      <c r="D242" s="11" t="n">
+        <v>95</v>
+      </c>
       <c r="E242" s="11" t="n">
-        <v>1.08</v>
+        <v>95</v>
       </c>
       <c r="F242" s="11">
         <f>IF(D242&lt;&gt;"",D242,IF(C242&lt;&gt;"",C242,""))</f>
@@ -9515,25 +9515,27 @@
         <f>IF(AND(C242&lt;&gt;"",D242&lt;&gt;""),IF(C242=0,"",D242/C242-1),"")</f>
         <v/>
       </c>
-      <c r="K242" s="5" t="n"/>
+      <c r="K242" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="5" t="inlineStr">
         <is>
-          <t>MONVA</t>
+          <t>MAXXIMO (MOLLETES)</t>
         </is>
       </c>
       <c r="B243" s="5" t="inlineStr">
         <is>
-          <t>GARRAFA AOVE MONTABES 10 L</t>
-        </is>
-      </c>
-      <c r="C243" s="11" t="n">
-        <v>57</v>
-      </c>
+          <t>MOLLETES (UD)</t>
+        </is>
+      </c>
+      <c r="C243" s="11" t="n"/>
       <c r="D243" s="11" t="n"/>
       <c r="E243" s="11" t="n">
-        <v>57</v>
+        <v>1.08</v>
       </c>
       <c r="F243" s="11">
         <f>IF(D243&lt;&gt;"",D243,IF(C243&lt;&gt;"",C243,""))</f>
@@ -9560,22 +9562,20 @@
     <row r="244">
       <c r="A244" s="5" t="inlineStr">
         <is>
-          <t>MUNDELA</t>
+          <t>MONVA</t>
         </is>
       </c>
       <c r="B244" s="5" t="inlineStr">
         <is>
-          <t>BARBADILLO VI MOSCATO FRIZZANTE</t>
+          <t>GARRAFA AOVE MONTABES 10 L</t>
         </is>
       </c>
       <c r="C244" s="11" t="n">
-        <v>5.63</v>
-      </c>
-      <c r="D244" s="11" t="n">
-        <v>5.63</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="D244" s="11" t="n"/>
       <c r="E244" s="11" t="n">
-        <v>5.63</v>
+        <v>57</v>
       </c>
       <c r="F244" s="11">
         <f>IF(D244&lt;&gt;"",D244,IF(C244&lt;&gt;"",C244,""))</f>
@@ -9607,13 +9607,17 @@
       </c>
       <c r="B245" s="5" t="inlineStr">
         <is>
-          <t>BOCACHANCLA TINTO JOVEN</t>
-        </is>
-      </c>
-      <c r="C245" s="11" t="n"/>
-      <c r="D245" s="11" t="n"/>
+          <t>BARBADILLO VI MOSCATO FRIZZANTE</t>
+        </is>
+      </c>
+      <c r="C245" s="11" t="n">
+        <v>5.63</v>
+      </c>
+      <c r="D245" s="11" t="n">
+        <v>5.63</v>
+      </c>
       <c r="E245" s="11" t="n">
-        <v>3.58</v>
+        <v>5.63</v>
       </c>
       <c r="F245" s="11">
         <f>IF(D245&lt;&gt;"",D245,IF(C245&lt;&gt;"",C245,""))</f>
@@ -9645,17 +9649,13 @@
       </c>
       <c r="B246" s="5" t="inlineStr">
         <is>
-          <t>CEPAS VELLAS GODEVAL</t>
-        </is>
-      </c>
-      <c r="C246" s="11" t="n">
-        <v>11.77</v>
-      </c>
-      <c r="D246" s="11" t="n">
-        <v>11.77</v>
-      </c>
+          <t>BOCACHANCLA TINTO JOVEN</t>
+        </is>
+      </c>
+      <c r="C246" s="11" t="n"/>
+      <c r="D246" s="11" t="n"/>
       <c r="E246" s="11" t="n">
-        <v>11.77</v>
+        <v>3.58</v>
       </c>
       <c r="F246" s="11">
         <f>IF(D246&lt;&gt;"",D246,IF(C246&lt;&gt;"",C246,""))</f>
@@ -9687,17 +9687,17 @@
       </c>
       <c r="B247" s="5" t="inlineStr">
         <is>
-          <t>CORIMBO</t>
+          <t>CEPAS VELLAS GODEVAL</t>
         </is>
       </c>
       <c r="C247" s="11" t="n">
-        <v>13.91</v>
+        <v>11.77</v>
       </c>
       <c r="D247" s="11" t="n">
-        <v>13.91</v>
+        <v>11.77</v>
       </c>
       <c r="E247" s="11" t="n">
-        <v>13.91</v>
+        <v>11.77</v>
       </c>
       <c r="F247" s="11">
         <f>IF(D247&lt;&gt;"",D247,IF(C247&lt;&gt;"",C247,""))</f>
@@ -9729,13 +9729,17 @@
       </c>
       <c r="B248" s="5" t="inlineStr">
         <is>
-          <t>GURPEGUI TINTO 3/4</t>
-        </is>
-      </c>
-      <c r="C248" s="11" t="n"/>
-      <c r="D248" s="11" t="n"/>
+          <t>CORIMBO</t>
+        </is>
+      </c>
+      <c r="C248" s="11" t="n">
+        <v>13.91</v>
+      </c>
+      <c r="D248" s="11" t="n">
+        <v>13.91</v>
+      </c>
       <c r="E248" s="11" t="n">
-        <v>2.82</v>
+        <v>13.91</v>
       </c>
       <c r="F248" s="11">
         <f>IF(D248&lt;&gt;"",D248,IF(C248&lt;&gt;"",C248,""))</f>
@@ -9767,14 +9771,14 @@
       </c>
       <c r="B249" s="5" t="inlineStr">
         <is>
-          <t>MANZANILLA SOLEAR 3/8</t>
+          <t>GURPEGUI TINTO 3/4</t>
         </is>
       </c>
       <c r="C249" s="11" t="n"/>
-      <c r="D249" s="11" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="E249" s="11" t="n"/>
+      <c r="D249" s="11" t="n"/>
+      <c r="E249" s="11" t="n">
+        <v>2.82</v>
+      </c>
       <c r="F249" s="11">
         <f>IF(D249&lt;&gt;"",D249,IF(C249&lt;&gt;"",C249,""))</f>
         <v/>
@@ -9805,16 +9809,14 @@
       </c>
       <c r="B250" s="5" t="inlineStr">
         <is>
-          <t>PACO GARCIA CRIANZA 3/4</t>
+          <t>MANZANILLA SOLEAR 3/8</t>
         </is>
       </c>
       <c r="C250" s="11" t="n"/>
       <c r="D250" s="11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="E250" s="11" t="n">
-        <v>5.3</v>
-      </c>
+        <v>4.42</v>
+      </c>
+      <c r="E250" s="11" t="n"/>
       <c r="F250" s="11">
         <f>IF(D250&lt;&gt;"",D250,IF(C250&lt;&gt;"",C250,""))</f>
         <v/>
@@ -9845,15 +9847,15 @@
       </c>
       <c r="B251" s="5" t="inlineStr">
         <is>
-          <t>R.B. EDI.LIM. EARLY HARVEST ROSADO</t>
-        </is>
-      </c>
-      <c r="C251" s="11" t="n">
-        <v>7.88</v>
-      </c>
-      <c r="D251" s="11" t="n"/>
+          <t>PACO GARCIA CRIANZA 3/4</t>
+        </is>
+      </c>
+      <c r="C251" s="11" t="n"/>
+      <c r="D251" s="11" t="n">
+        <v>5.3</v>
+      </c>
       <c r="E251" s="11" t="n">
-        <v>7.88</v>
+        <v>5.3</v>
       </c>
       <c r="F251" s="11">
         <f>IF(D251&lt;&gt;"",D251,IF(C251&lt;&gt;"",C251,""))</f>
@@ -9885,17 +9887,15 @@
       </c>
       <c r="B252" s="5" t="inlineStr">
         <is>
-          <t>RAMON BILBAO BLANCO VERDEJO 3/4</t>
+          <t>R.B. EDI.LIM. EARLY HARVEST ROSADO</t>
         </is>
       </c>
       <c r="C252" s="11" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="D252" s="11" t="n">
-        <v>4.67</v>
-      </c>
+        <v>7.88</v>
+      </c>
+      <c r="D252" s="11" t="n"/>
       <c r="E252" s="11" t="n">
-        <v>4.67</v>
+        <v>7.88</v>
       </c>
       <c r="F252" s="11">
         <f>IF(D252&lt;&gt;"",D252,IF(C252&lt;&gt;"",C252,""))</f>
@@ -9927,17 +9927,17 @@
       </c>
       <c r="B253" s="5" t="inlineStr">
         <is>
-          <t>RAMON BILBAO VIÑEDOS DE ALTURA 3/4</t>
+          <t>RAMON BILBAO BLANCO VERDEJO 3/4</t>
         </is>
       </c>
       <c r="C253" s="11" t="n">
-        <v>8.779999999999999</v>
+        <v>4.67</v>
       </c>
       <c r="D253" s="11" t="n">
-        <v>8.779999999999999</v>
+        <v>4.67</v>
       </c>
       <c r="E253" s="11" t="n">
-        <v>8.779999999999999</v>
+        <v>4.67</v>
       </c>
       <c r="F253" s="11">
         <f>IF(D253&lt;&gt;"",D253,IF(C253&lt;&gt;"",C253,""))</f>
@@ -9969,14 +9969,18 @@
       </c>
       <c r="B254" s="5" t="inlineStr">
         <is>
-          <t>RODA RESERVA 3/4</t>
+          <t>RAMON BILBAO VIÑEDOS DE ALTURA 3/4</t>
         </is>
       </c>
       <c r="C254" s="11" t="n">
-        <v>21.38</v>
-      </c>
-      <c r="D254" s="11" t="n"/>
-      <c r="E254" s="11" t="n"/>
+        <v>8.779999999999999</v>
+      </c>
+      <c r="D254" s="11" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="E254" s="11" t="n">
+        <v>8.779999999999999</v>
+      </c>
       <c r="F254" s="11">
         <f>IF(D254&lt;&gt;"",D254,IF(C254&lt;&gt;"",C254,""))</f>
         <v/>
@@ -10007,15 +10011,13 @@
       </c>
       <c r="B255" s="5" t="inlineStr">
         <is>
-          <t>VINAGRE DE JEREZ RESERVA AL MOSCATEL</t>
+          <t>RODA RESERVA 3/4</t>
         </is>
       </c>
       <c r="C255" s="11" t="n">
-        <v>5.44</v>
-      </c>
-      <c r="D255" s="11" t="n">
-        <v>5.44</v>
-      </c>
+        <v>21.38</v>
+      </c>
+      <c r="D255" s="11" t="n"/>
       <c r="E255" s="11" t="n"/>
       <c r="F255" s="11">
         <f>IF(D255&lt;&gt;"",D255,IF(C255&lt;&gt;"",C255,""))</f>
@@ -10042,23 +10044,21 @@
     <row r="256">
       <c r="A256" s="5" t="inlineStr">
         <is>
-          <t>PATATAS YAGO</t>
+          <t>MUNDELA</t>
         </is>
       </c>
       <c r="B256" s="5" t="inlineStr">
         <is>
-          <t>SACO AGRIA NUEVA ALICANTE</t>
+          <t>VINAGRE DE JEREZ RESERVA AL MOSCATEL</t>
         </is>
       </c>
       <c r="C256" s="11" t="n">
-        <v>0.95</v>
+        <v>5.44</v>
       </c>
       <c r="D256" s="11" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E256" s="11" t="n">
-        <v>0.88</v>
-      </c>
+        <v>5.44</v>
+      </c>
+      <c r="E256" s="11" t="n"/>
       <c r="F256" s="11">
         <f>IF(D256&lt;&gt;"",D256,IF(C256&lt;&gt;"",C256,""))</f>
         <v/>
@@ -10079,11 +10079,7 @@
         <f>IF(AND(C256&lt;&gt;"",D256&lt;&gt;""),IF(C256=0,"",D256/C256-1),"")</f>
         <v/>
       </c>
-      <c r="K256" s="5" t="inlineStr">
-        <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 0,88 / 0,89 / 0,95. Desde el 24/09 el albarán pone «saco agria Alicante» (sin «nueva»)</t>
-        </is>
-      </c>
+      <c r="K256" s="5" t="n"/>
     </row>
     <row r="257">
       <c r="A257" s="5" t="inlineStr">
@@ -10093,17 +10089,17 @@
       </c>
       <c r="B257" s="5" t="inlineStr">
         <is>
-          <t>SACO MONALISA</t>
+          <t>SACO AGRIA NUEVA ALICANTE</t>
         </is>
       </c>
       <c r="C257" s="11" t="n">
-        <v>0.93</v>
+        <v>0.95</v>
       </c>
       <c r="D257" s="11" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="E257" s="11" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="F257" s="11">
         <f>IF(D257&lt;&gt;"",D257,IF(C257&lt;&gt;"",C257,""))</f>
@@ -10127,29 +10123,29 @@
       </c>
       <c r="K257" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 0,83 / 0,90 / 0,93. Varios precios en agosto: 0,88 / 0,93</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 0,88 / 0,89 / 0,95. Desde el 24/09 el albarán pone «saco agria Alicante» (sin «nueva»)</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="5" t="inlineStr">
         <is>
-          <t>PESCADERIA PALACIO</t>
+          <t>PATATAS YAGO</t>
         </is>
       </c>
       <c r="B258" s="5" t="inlineStr">
         <is>
-          <t>ALISTADO 15/20 PARAPENAEUS</t>
+          <t>SACO MONALISA</t>
         </is>
       </c>
       <c r="C258" s="11" t="n">
-        <v>48</v>
+        <v>0.93</v>
       </c>
       <c r="D258" s="11" t="n">
-        <v>48</v>
+        <v>0.93</v>
       </c>
       <c r="E258" s="11" t="n">
-        <v>48</v>
+        <v>0.93</v>
       </c>
       <c r="F258" s="11">
         <f>IF(D258&lt;&gt;"",D258,IF(C258&lt;&gt;"",C258,""))</f>
@@ -10173,28 +10169,30 @@
       </c>
       <c r="K258" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 0,83 / 0,90 / 0,93. Varios precios en agosto: 0,88 / 0,93</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="5" t="inlineStr">
         <is>
-          <t>PESCARUM</t>
+          <t>PESCADERIA PALACIO</t>
         </is>
       </c>
       <c r="B259" s="5" t="inlineStr">
         <is>
-          <t>ALISTADOS</t>
+          <t>ALISTADO 15/20 PARAPENAEUS</t>
         </is>
       </c>
       <c r="C259" s="11" t="n">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D259" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="E259" s="11" t="n"/>
+        <v>48</v>
+      </c>
+      <c r="E259" s="11" t="n">
+        <v>48</v>
+      </c>
       <c r="F259" s="11">
         <f>IF(D259&lt;&gt;"",D259,IF(C259&lt;&gt;"",C259,""))</f>
         <v/>
@@ -10229,18 +10227,16 @@
       </c>
       <c r="B260" s="5" t="inlineStr">
         <is>
-          <t>CALAMARES</t>
+          <t>ALISTADOS</t>
         </is>
       </c>
       <c r="C260" s="11" t="n">
-        <v>21.5</v>
+        <v>78</v>
       </c>
       <c r="D260" s="11" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="E260" s="11" t="n">
-        <v>21.5</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="E260" s="11" t="n"/>
       <c r="F260" s="11">
         <f>IF(D260&lt;&gt;"",D260,IF(C260&lt;&gt;"",C260,""))</f>
         <v/>
@@ -10275,17 +10271,17 @@
       </c>
       <c r="B261" s="5" t="inlineStr">
         <is>
-          <t>CARABINEROS</t>
+          <t>CALAMARES</t>
         </is>
       </c>
       <c r="C261" s="11" t="n">
-        <v>98</v>
+        <v>21.5</v>
       </c>
       <c r="D261" s="11" t="n">
-        <v>98</v>
+        <v>21.5</v>
       </c>
       <c r="E261" s="11" t="n">
-        <v>120</v>
+        <v>21.5</v>
       </c>
       <c r="F261" s="11">
         <f>IF(D261&lt;&gt;"",D261,IF(C261&lt;&gt;"",C261,""))</f>
@@ -10321,15 +10317,17 @@
       </c>
       <c r="B262" s="5" t="inlineStr">
         <is>
-          <t>CIGALA</t>
+          <t>CARABINEROS</t>
         </is>
       </c>
       <c r="C262" s="11" t="n">
-        <v>75</v>
-      </c>
-      <c r="D262" s="11" t="n"/>
+        <v>98</v>
+      </c>
+      <c r="D262" s="11" t="n">
+        <v>98</v>
+      </c>
       <c r="E262" s="11" t="n">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="F262" s="11">
         <f>IF(D262&lt;&gt;"",D262,IF(C262&lt;&gt;"",C262,""))</f>
@@ -10365,15 +10363,15 @@
       </c>
       <c r="B263" s="5" t="inlineStr">
         <is>
-          <t>COCOCHAS</t>
-        </is>
-      </c>
-      <c r="C263" s="11" t="n"/>
-      <c r="D263" s="11" t="n">
-        <v>60</v>
-      </c>
+          <t>CIGALA</t>
+        </is>
+      </c>
+      <c r="C263" s="11" t="n">
+        <v>75</v>
+      </c>
+      <c r="D263" s="11" t="n"/>
       <c r="E263" s="11" t="n">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="F263" s="11">
         <f>IF(D263&lt;&gt;"",D263,IF(C263&lt;&gt;"",C263,""))</f>
@@ -10397,7 +10395,7 @@
       </c>
       <c r="K263" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 58,00 / 60,00</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -10409,17 +10407,15 @@
       </c>
       <c r="B264" s="5" t="inlineStr">
         <is>
-          <t>COQUINAS</t>
-        </is>
-      </c>
-      <c r="C264" s="11" t="n">
-        <v>30</v>
-      </c>
+          <t>COCOCHAS</t>
+        </is>
+      </c>
+      <c r="C264" s="11" t="n"/>
       <c r="D264" s="11" t="n">
-        <v>32.5</v>
+        <v>60</v>
       </c>
       <c r="E264" s="11" t="n">
-        <v>32.5</v>
+        <v>60</v>
       </c>
       <c r="F264" s="11">
         <f>IF(D264&lt;&gt;"",D264,IF(C264&lt;&gt;"",C264,""))</f>
@@ -10443,7 +10439,7 @@
       </c>
       <c r="K264" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 30,00 / 32,50</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 58,00 / 60,00</t>
         </is>
       </c>
     </row>
@@ -10455,15 +10451,17 @@
       </c>
       <c r="B265" s="5" t="inlineStr">
         <is>
-          <t>LANGOSTINO</t>
+          <t>COQUINAS</t>
         </is>
       </c>
       <c r="C265" s="11" t="n">
-        <v>35</v>
-      </c>
-      <c r="D265" s="11" t="n"/>
+        <v>30</v>
+      </c>
+      <c r="D265" s="11" t="n">
+        <v>32.5</v>
+      </c>
       <c r="E265" s="11" t="n">
-        <v>35</v>
+        <v>32.5</v>
       </c>
       <c r="F265" s="11">
         <f>IF(D265&lt;&gt;"",D265,IF(C265&lt;&gt;"",C265,""))</f>
@@ -10487,7 +10485,7 @@
       </c>
       <c r="K265" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 30,00 / 32,50</t>
         </is>
       </c>
     </row>
@@ -10499,17 +10497,15 @@
       </c>
       <c r="B266" s="5" t="inlineStr">
         <is>
-          <t>NAVAJA</t>
+          <t>LANGOSTINO</t>
         </is>
       </c>
       <c r="C266" s="11" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="D266" s="11" t="n">
-        <v>25</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D266" s="11" t="n"/>
       <c r="E266" s="11" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F266" s="11">
         <f>IF(D266&lt;&gt;"",D266,IF(C266&lt;&gt;"",C266,""))</f>
@@ -10533,7 +10529,7 @@
       </c>
       <c r="K266" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 23,00 / 25,00 / 25,50 / 29,50. Varios precios en septiembre: 22,00 / 23,00 / 23,50 / 24,00 / 25,00</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -10545,13 +10541,17 @@
       </c>
       <c r="B267" s="5" t="inlineStr">
         <is>
-          <t>OSTRAS (UD)</t>
-        </is>
-      </c>
-      <c r="C267" s="11" t="n"/>
-      <c r="D267" s="11" t="n"/>
+          <t>NAVAJA</t>
+        </is>
+      </c>
+      <c r="C267" s="11" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D267" s="11" t="n">
+        <v>25</v>
+      </c>
       <c r="E267" s="11" t="n">
-        <v>2.5</v>
+        <v>25</v>
       </c>
       <c r="F267" s="11">
         <f>IF(D267&lt;&gt;"",D267,IF(C267&lt;&gt;"",C267,""))</f>
@@ -10575,7 +10575,7 @@
       </c>
       <c r="K267" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 23,00 / 25,00 / 25,50 / 29,50. Varios precios en septiembre: 22,00 / 23,00 / 23,50 / 24,00 / 25,00</t>
         </is>
       </c>
     </row>
@@ -10587,14 +10587,14 @@
       </c>
       <c r="B268" s="5" t="inlineStr">
         <is>
-          <t>PARRILLATO</t>
+          <t>OSTRAS (UD)</t>
         </is>
       </c>
       <c r="C268" s="11" t="n"/>
-      <c r="D268" s="11" t="n">
-        <v>14</v>
-      </c>
-      <c r="E268" s="11" t="n"/>
+      <c r="D268" s="11" t="n"/>
+      <c r="E268" s="11" t="n">
+        <v>2.5</v>
+      </c>
       <c r="F268" s="11">
         <f>IF(D268&lt;&gt;"",D268,IF(C268&lt;&gt;"",C268,""))</f>
         <v/>
@@ -10629,14 +10629,14 @@
       </c>
       <c r="B269" s="5" t="inlineStr">
         <is>
-          <t>PERIQUITO</t>
+          <t>PARRILLATO</t>
         </is>
       </c>
       <c r="C269" s="11" t="n"/>
-      <c r="D269" s="11" t="n"/>
-      <c r="E269" s="11" t="n">
-        <v>13.5</v>
-      </c>
+      <c r="D269" s="11" t="n">
+        <v>14</v>
+      </c>
+      <c r="E269" s="11" t="n"/>
       <c r="F269" s="11">
         <f>IF(D269&lt;&gt;"",D269,IF(C269&lt;&gt;"",C269,""))</f>
         <v/>
@@ -10659,7 +10659,7 @@
       </c>
       <c r="K269" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Lectura dudosa en el albarán del 29/09</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -10671,17 +10671,13 @@
       </c>
       <c r="B270" s="5" t="inlineStr">
         <is>
-          <t>PULPO</t>
-        </is>
-      </c>
-      <c r="C270" s="11" t="n">
-        <v>30.5</v>
-      </c>
-      <c r="D270" s="11" t="n">
-        <v>30.5</v>
-      </c>
+          <t>PERIQUITO</t>
+        </is>
+      </c>
+      <c r="C270" s="11" t="n"/>
+      <c r="D270" s="11" t="n"/>
       <c r="E270" s="11" t="n">
-        <v>30.5</v>
+        <v>13.5</v>
       </c>
       <c r="F270" s="11">
         <f>IF(D270&lt;&gt;"",D270,IF(C270&lt;&gt;"",C270,""))</f>
@@ -10705,7 +10701,7 @@
       </c>
       <c r="K270" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Lectura dudosa en el albarán del 29/09</t>
         </is>
       </c>
     </row>
@@ -10717,14 +10713,18 @@
       </c>
       <c r="B271" s="5" t="inlineStr">
         <is>
-          <t>QUISQUILLA</t>
+          <t>PULPO</t>
         </is>
       </c>
       <c r="C271" s="11" t="n">
-        <v>59</v>
-      </c>
-      <c r="D271" s="11" t="n"/>
-      <c r="E271" s="11" t="n"/>
+        <v>30.5</v>
+      </c>
+      <c r="D271" s="11" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="E271" s="11" t="n">
+        <v>30.5</v>
+      </c>
       <c r="F271" s="11">
         <f>IF(D271&lt;&gt;"",D271,IF(C271&lt;&gt;"",C271,""))</f>
         <v/>
@@ -10747,7 +10747,7 @@
       </c>
       <c r="K271" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 58,00 / 59,00</t>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
         </is>
       </c>
     </row>
@@ -10759,18 +10759,14 @@
       </c>
       <c r="B272" s="5" t="inlineStr">
         <is>
-          <t>ZAMBURIÑAS</t>
+          <t>QUISQUILLA</t>
         </is>
       </c>
       <c r="C272" s="11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="D272" s="11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="E272" s="11" t="n">
-        <v>15.5</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D272" s="11" t="n"/>
+      <c r="E272" s="11" t="n"/>
       <c r="F272" s="11">
         <f>IF(D272&lt;&gt;"",D272,IF(C272&lt;&gt;"",C272,""))</f>
         <v/>
@@ -10793,29 +10789,29 @@
       </c>
       <c r="K272" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en julio: 58,00 / 59,00</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="5" t="inlineStr">
         <is>
-          <t>PEÑALASTALLAS</t>
+          <t>PESCARUM</t>
         </is>
       </c>
       <c r="B273" s="5" t="inlineStr">
         <is>
-          <t>MOLLEJAS DE CORDERO</t>
+          <t>ZAMBURIÑAS</t>
         </is>
       </c>
       <c r="C273" s="11" t="n">
-        <v>27.9</v>
+        <v>15.5</v>
       </c>
       <c r="D273" s="11" t="n">
-        <v>27.9</v>
+        <v>15.5</v>
       </c>
       <c r="E273" s="11" t="n">
-        <v>27.9</v>
+        <v>15.5</v>
       </c>
       <c r="F273" s="11">
         <f>IF(D273&lt;&gt;"",D273,IF(C273&lt;&gt;"",C273,""))</f>
@@ -10837,7 +10833,11 @@
         <f>IF(AND(C273&lt;&gt;"",D273&lt;&gt;""),IF(C273=0,"",D273/C273-1),"")</f>
         <v/>
       </c>
-      <c r="K273" s="5" t="n"/>
+      <c r="K273" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="5" t="inlineStr">
@@ -10847,17 +10847,17 @@
       </c>
       <c r="B274" s="5" t="inlineStr">
         <is>
-          <t>PINCHO MORUNO DE POLLO</t>
+          <t>MOLLEJAS DE CORDERO</t>
         </is>
       </c>
       <c r="C274" s="11" t="n">
-        <v>8.9</v>
+        <v>27.9</v>
       </c>
       <c r="D274" s="11" t="n">
-        <v>8.9</v>
+        <v>27.9</v>
       </c>
       <c r="E274" s="11" t="n">
-        <v>8.9</v>
+        <v>27.9</v>
       </c>
       <c r="F274" s="11">
         <f>IF(D274&lt;&gt;"",D274,IF(C274&lt;&gt;"",C274,""))</f>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="B275" s="5" t="inlineStr">
         <is>
-          <t>PINCHOS MORUNOS</t>
+          <t>PINCHO MORUNO DE POLLO</t>
         </is>
       </c>
       <c r="C275" s="11" t="n">
@@ -10931,14 +10931,18 @@
       </c>
       <c r="B276" s="5" t="inlineStr">
         <is>
-          <t>POLLOS ENTEROS</t>
+          <t>PINCHOS MORUNOS</t>
         </is>
       </c>
       <c r="C276" s="11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D276" s="11" t="n"/>
-      <c r="E276" s="11" t="n"/>
+        <v>8.9</v>
+      </c>
+      <c r="D276" s="11" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="E276" s="11" t="n">
+        <v>8.9</v>
+      </c>
       <c r="F276" s="11">
         <f>IF(D276&lt;&gt;"",D276,IF(C276&lt;&gt;"",C276,""))</f>
         <v/>
@@ -10964,19 +10968,19 @@
     <row r="277">
       <c r="A277" s="5" t="inlineStr">
         <is>
-          <t>REGERE AOVE</t>
+          <t>PEÑALASTALLAS</t>
         </is>
       </c>
       <c r="B277" s="5" t="inlineStr">
         <is>
-          <t>CAJA 6 UDS "SELECTO" AOVE 500 ML VIDRIO</t>
-        </is>
-      </c>
-      <c r="C277" s="11" t="n"/>
+          <t>POLLOS ENTEROS</t>
+        </is>
+      </c>
+      <c r="C277" s="11" t="n">
+        <v>3.75</v>
+      </c>
       <c r="D277" s="11" t="n"/>
-      <c r="E277" s="11" t="n">
-        <v>69</v>
-      </c>
+      <c r="E277" s="11" t="n"/>
       <c r="F277" s="11">
         <f>IF(D277&lt;&gt;"",D277,IF(C277&lt;&gt;"",C277,""))</f>
         <v/>
@@ -11007,7 +11011,7 @@
       </c>
       <c r="B278" s="5" t="inlineStr">
         <is>
-          <t>CAJA 6 UDS BOTELLA 1L "SELECCION DEL CHEF" AOVE</t>
+          <t>CAJA 6 UDS "SELECTO" AOVE 500 ML VIDRIO</t>
         </is>
       </c>
       <c r="C278" s="11" t="n"/>
@@ -11040,22 +11044,18 @@
     <row r="279">
       <c r="A279" s="5" t="inlineStr">
         <is>
-          <t>ROMERO ALVAREZ</t>
+          <t>REGERE AOVE</t>
         </is>
       </c>
       <c r="B279" s="5" t="inlineStr">
         <is>
-          <t>PRESA 100% IBERICA</t>
-        </is>
-      </c>
-      <c r="C279" s="11" t="n">
-        <v>25.2</v>
-      </c>
-      <c r="D279" s="11" t="n">
-        <v>25.2</v>
-      </c>
+          <t>CAJA 6 UDS BOTELLA 1L "SELECCION DEL CHEF" AOVE</t>
+        </is>
+      </c>
+      <c r="C279" s="11" t="n"/>
+      <c r="D279" s="11" t="n"/>
       <c r="E279" s="11" t="n">
-        <v>25.2</v>
+        <v>69</v>
       </c>
       <c r="F279" s="11">
         <f>IF(D279&lt;&gt;"",D279,IF(C279&lt;&gt;"",C279,""))</f>
@@ -11087,10 +11087,12 @@
       </c>
       <c r="B280" s="5" t="inlineStr">
         <is>
-          <t>PRESA IBERICA</t>
-        </is>
-      </c>
-      <c r="C280" s="11" t="n"/>
+          <t>PRESA 100% IBERICA</t>
+        </is>
+      </c>
+      <c r="C280" s="11" t="n">
+        <v>25.2</v>
+      </c>
       <c r="D280" s="11" t="n">
         <v>25.2</v>
       </c>
@@ -11122,18 +11124,20 @@
     <row r="281">
       <c r="A281" s="5" t="inlineStr">
         <is>
-          <t>SENSORVISION</t>
+          <t>ROMERO ALVAREZ</t>
         </is>
       </c>
       <c r="B281" s="5" t="inlineStr">
         <is>
-          <t>CAJA PAPEL TERMICO 80X80</t>
+          <t>PRESA IBERICA</t>
         </is>
       </c>
       <c r="C281" s="11" t="n"/>
-      <c r="D281" s="11" t="n"/>
+      <c r="D281" s="11" t="n">
+        <v>25.2</v>
+      </c>
       <c r="E281" s="11" t="n">
-        <v>49</v>
+        <v>25.2</v>
       </c>
       <c r="F281" s="11">
         <f>IF(D281&lt;&gt;"",D281,IF(C281&lt;&gt;"",C281,""))</f>
@@ -11160,22 +11164,18 @@
     <row r="282">
       <c r="A282" s="5" t="inlineStr">
         <is>
-          <t>SUBMARINER</t>
+          <t>SENSORVISION</t>
         </is>
       </c>
       <c r="B282" s="5" t="inlineStr">
         <is>
-          <t>ABSOLUT 0,70L</t>
-        </is>
-      </c>
-      <c r="C282" s="11" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="D282" s="11" t="n">
-        <v>11.38</v>
-      </c>
+          <t>CAJA PAPEL TERMICO 80X80</t>
+        </is>
+      </c>
+      <c r="C282" s="11" t="n"/>
+      <c r="D282" s="11" t="n"/>
       <c r="E282" s="11" t="n">
-        <v>11.38</v>
+        <v>49</v>
       </c>
       <c r="F282" s="11">
         <f>IF(D282&lt;&gt;"",D282,IF(C282&lt;&gt;"",C282,""))</f>
@@ -11197,11 +11197,7 @@
         <f>IF(AND(C282&lt;&gt;"",D282&lt;&gt;""),IF(C282=0,"",D282/C282-1),"")</f>
         <v/>
       </c>
-      <c r="K282" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 11,85 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K282" s="5" t="n"/>
     </row>
     <row r="283">
       <c r="A283" s="5" t="inlineStr">
@@ -11211,15 +11207,17 @@
       </c>
       <c r="B283" s="5" t="inlineStr">
         <is>
-          <t>AGT 3L MOS DE PAS</t>
+          <t>ABSOLUT 0,70L</t>
         </is>
       </c>
       <c r="C283" s="11" t="n">
-        <v>19.18</v>
-      </c>
-      <c r="D283" s="11" t="n"/>
+        <v>11.38</v>
+      </c>
+      <c r="D283" s="11" t="n">
+        <v>11.38</v>
+      </c>
       <c r="E283" s="11" t="n">
-        <v>19.18</v>
+        <v>11.38</v>
       </c>
       <c r="F283" s="11">
         <f>IF(D283&lt;&gt;"",D283,IF(C283&lt;&gt;"",C283,""))</f>
@@ -11243,7 +11241,7 @@
       </c>
       <c r="K283" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 19,98 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 11,85 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11255,17 +11253,15 @@
       </c>
       <c r="B284" s="5" t="inlineStr">
         <is>
-          <t>APEROL LITRO</t>
+          <t>AGT 3L MOS DE PAS</t>
         </is>
       </c>
       <c r="C284" s="11" t="n">
-        <v>10.72</v>
-      </c>
-      <c r="D284" s="11" t="n">
-        <v>10.72</v>
-      </c>
+        <v>19.18</v>
+      </c>
+      <c r="D284" s="11" t="n"/>
       <c r="E284" s="11" t="n">
-        <v>10.72</v>
+        <v>19.18</v>
       </c>
       <c r="F284" s="11">
         <f>IF(D284&lt;&gt;"",D284,IF(C284&lt;&gt;"",C284,""))</f>
@@ -11289,7 +11285,7 @@
       </c>
       <c r="K284" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 11,17 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 19,98 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11301,13 +11297,17 @@
       </c>
       <c r="B285" s="5" t="inlineStr">
         <is>
-          <t>BACARDI 1L NR</t>
-        </is>
-      </c>
-      <c r="C285" s="11" t="n"/>
-      <c r="D285" s="11" t="n"/>
+          <t>APEROL LITRO</t>
+        </is>
+      </c>
+      <c r="C285" s="11" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="D285" s="11" t="n">
+        <v>10.72</v>
+      </c>
       <c r="E285" s="11" t="n">
-        <v>13.14</v>
+        <v>10.72</v>
       </c>
       <c r="F285" s="11">
         <f>IF(D285&lt;&gt;"",D285,IF(C285&lt;&gt;"",C285,""))</f>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="K285" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 13,69 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 11,17 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11343,14 +11343,14 @@
       </c>
       <c r="B286" s="5" t="inlineStr">
         <is>
-          <t>BALLANTINES 0,70L NR</t>
-        </is>
-      </c>
-      <c r="C286" s="11" t="n">
-        <v>11.09</v>
-      </c>
+          <t>BACARDI 1L NR</t>
+        </is>
+      </c>
+      <c r="C286" s="11" t="n"/>
       <c r="D286" s="11" t="n"/>
-      <c r="E286" s="11" t="n"/>
+      <c r="E286" s="11" t="n">
+        <v>13.14</v>
+      </c>
       <c r="F286" s="11">
         <f>IF(D286&lt;&gt;"",D286,IF(C286&lt;&gt;"",C286,""))</f>
         <v/>
@@ -11371,7 +11371,11 @@
         <f>IF(AND(C286&lt;&gt;"",D286&lt;&gt;""),IF(C286=0,"",D286/C286-1),"")</f>
         <v/>
       </c>
-      <c r="K286" s="5" t="n"/>
+      <c r="K286" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 13,69 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="5" t="inlineStr">
@@ -11381,16 +11385,14 @@
       </c>
       <c r="B287" s="5" t="inlineStr">
         <is>
-          <t>BEEFEATER 0,70L NR</t>
+          <t>BALLANTINES 0,70L NR</t>
         </is>
       </c>
       <c r="C287" s="11" t="n">
-        <v>11.81</v>
+        <v>11.09</v>
       </c>
       <c r="D287" s="11" t="n"/>
-      <c r="E287" s="11" t="n">
-        <v>11.81</v>
-      </c>
+      <c r="E287" s="11" t="n"/>
       <c r="F287" s="11">
         <f>IF(D287&lt;&gt;"",D287,IF(C287&lt;&gt;"",C287,""))</f>
         <v/>
@@ -11411,11 +11413,7 @@
         <f>IF(AND(C287&lt;&gt;"",D287&lt;&gt;""),IF(C287=0,"",D287/C287-1),"")</f>
         <v/>
       </c>
-      <c r="K287" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 12,30 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K287" s="5" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="5" t="inlineStr">
@@ -11425,15 +11423,15 @@
       </c>
       <c r="B288" s="5" t="inlineStr">
         <is>
-          <t>BOMBAY SAPHIRE 0,70</t>
+          <t>BEEFEATER 0,70L NR</t>
         </is>
       </c>
       <c r="C288" s="11" t="n">
-        <v>13.63</v>
+        <v>11.81</v>
       </c>
       <c r="D288" s="11" t="n"/>
       <c r="E288" s="11" t="n">
-        <v>13.63</v>
+        <v>11.81</v>
       </c>
       <c r="F288" s="11">
         <f>IF(D288&lt;&gt;"",D288,IF(C288&lt;&gt;"",C288,""))</f>
@@ -11457,7 +11455,7 @@
       </c>
       <c r="K288" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 14,20 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 12,30 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11469,14 +11467,16 @@
       </c>
       <c r="B289" s="5" t="inlineStr">
         <is>
-          <t>BRUGAL 0,70L NR</t>
+          <t>BOMBAY SAPHIRE 0,70</t>
         </is>
       </c>
       <c r="C289" s="11" t="n">
-        <v>11.19</v>
+        <v>13.63</v>
       </c>
       <c r="D289" s="11" t="n"/>
-      <c r="E289" s="11" t="n"/>
+      <c r="E289" s="11" t="n">
+        <v>13.63</v>
+      </c>
       <c r="F289" s="11">
         <f>IF(D289&lt;&gt;"",D289,IF(C289&lt;&gt;"",C289,""))</f>
         <v/>
@@ -11497,7 +11497,11 @@
         <f>IF(AND(C289&lt;&gt;"",D289&lt;&gt;""),IF(C289=0,"",D289/C289-1),"")</f>
         <v/>
       </c>
-      <c r="K289" s="5" t="n"/>
+      <c r="K289" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 14,20 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="5" t="inlineStr">
@@ -11507,11 +11511,11 @@
       </c>
       <c r="B290" s="5" t="inlineStr">
         <is>
-          <t>BULLEIT BOURBON 0,70</t>
+          <t>BRUGAL 0,70L NR</t>
         </is>
       </c>
       <c r="C290" s="11" t="n">
-        <v>19.13</v>
+        <v>11.19</v>
       </c>
       <c r="D290" s="11" t="n"/>
       <c r="E290" s="11" t="n"/>
@@ -11545,14 +11549,14 @@
       </c>
       <c r="B291" s="5" t="inlineStr">
         <is>
-          <t>CAMPARI 1L</t>
-        </is>
-      </c>
-      <c r="C291" s="11" t="n"/>
+          <t>BULLEIT BOURBON 0,70</t>
+        </is>
+      </c>
+      <c r="C291" s="11" t="n">
+        <v>19.13</v>
+      </c>
       <c r="D291" s="11" t="n"/>
-      <c r="E291" s="11" t="n">
-        <v>14.02</v>
-      </c>
+      <c r="E291" s="11" t="n"/>
       <c r="F291" s="11">
         <f>IF(D291&lt;&gt;"",D291,IF(C291&lt;&gt;"",C291,""))</f>
         <v/>
@@ -11573,11 +11577,7 @@
         <f>IF(AND(C291&lt;&gt;"",D291&lt;&gt;""),IF(C291=0,"",D291/C291-1),"")</f>
         <v/>
       </c>
-      <c r="K291" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 14,60 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K291" s="5" t="n"/>
     </row>
     <row r="292">
       <c r="A292" s="5" t="inlineStr">
@@ -11587,14 +11587,14 @@
       </c>
       <c r="B292" s="5" t="inlineStr">
         <is>
-          <t>CHIVAS 12 AÑOS 0,7L NR</t>
-        </is>
-      </c>
-      <c r="C292" s="11" t="n">
-        <v>22.11</v>
-      </c>
+          <t>CAMPARI 1L</t>
+        </is>
+      </c>
+      <c r="C292" s="11" t="n"/>
       <c r="D292" s="11" t="n"/>
-      <c r="E292" s="11" t="n"/>
+      <c r="E292" s="11" t="n">
+        <v>14.02</v>
+      </c>
       <c r="F292" s="11">
         <f>IF(D292&lt;&gt;"",D292,IF(C292&lt;&gt;"",C292,""))</f>
         <v/>
@@ -11615,7 +11615,11 @@
         <f>IF(AND(C292&lt;&gt;"",D292&lt;&gt;""),IF(C292=0,"",D292/C292-1),"")</f>
         <v/>
       </c>
-      <c r="K292" s="5" t="n"/>
+      <c r="K292" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 14,60 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="5" t="inlineStr">
@@ -11625,16 +11629,14 @@
       </c>
       <c r="B293" s="5" t="inlineStr">
         <is>
-          <t>CINZANO PROSECCO SPRITZ</t>
+          <t>CHIVAS 12 AÑOS 0,7L NR</t>
         </is>
       </c>
       <c r="C293" s="11" t="n">
-        <v>4.83</v>
+        <v>22.11</v>
       </c>
       <c r="D293" s="11" t="n"/>
-      <c r="E293" s="11" t="n">
-        <v>4.83</v>
-      </c>
+      <c r="E293" s="11" t="n"/>
       <c r="F293" s="11">
         <f>IF(D293&lt;&gt;"",D293,IF(C293&lt;&gt;"",C293,""))</f>
         <v/>
@@ -11655,11 +11657,7 @@
         <f>IF(AND(C293&lt;&gt;"",D293&lt;&gt;""),IF(C293=0,"",D293/C293-1),"")</f>
         <v/>
       </c>
-      <c r="K293" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 5,03 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K293" s="5" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="5" t="inlineStr">
@@ -11669,17 +11667,15 @@
       </c>
       <c r="B294" s="5" t="inlineStr">
         <is>
-          <t>CREMA ORUJO 3L MOS DE PAS</t>
+          <t>CINZANO PROSECCO SPRITZ</t>
         </is>
       </c>
       <c r="C294" s="11" t="n">
-        <v>14.98</v>
-      </c>
-      <c r="D294" s="11" t="n">
-        <v>14.98</v>
-      </c>
+        <v>4.83</v>
+      </c>
+      <c r="D294" s="11" t="n"/>
       <c r="E294" s="11" t="n">
-        <v>14.98</v>
+        <v>4.83</v>
       </c>
       <c r="F294" s="11">
         <f>IF(D294&lt;&gt;"",D294,IF(C294&lt;&gt;"",C294,""))</f>
@@ -11703,7 +11699,7 @@
       </c>
       <c r="K294" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 15,60 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 5,03 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11715,14 +11711,18 @@
       </c>
       <c r="B295" s="5" t="inlineStr">
         <is>
-          <t>DYC 1L</t>
+          <t>CREMA ORUJO 3L MOS DE PAS</t>
         </is>
       </c>
       <c r="C295" s="11" t="n">
-        <v>10.68</v>
-      </c>
-      <c r="D295" s="11" t="n"/>
-      <c r="E295" s="11" t="n"/>
+        <v>14.98</v>
+      </c>
+      <c r="D295" s="11" t="n">
+        <v>14.98</v>
+      </c>
+      <c r="E295" s="11" t="n">
+        <v>14.98</v>
+      </c>
       <c r="F295" s="11">
         <f>IF(D295&lt;&gt;"",D295,IF(C295&lt;&gt;"",C295,""))</f>
         <v/>
@@ -11743,7 +11743,11 @@
         <f>IF(AND(C295&lt;&gt;"",D295&lt;&gt;""),IF(C295=0,"",D295/C295-1),"")</f>
         <v/>
       </c>
-      <c r="K295" s="5" t="n"/>
+      <c r="K295" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 15,60 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="5" t="inlineStr">
@@ -11753,14 +11757,14 @@
       </c>
       <c r="B296" s="5" t="inlineStr">
         <is>
-          <t>FERNET BRANCA 0,70L</t>
-        </is>
-      </c>
-      <c r="C296" s="11" t="n"/>
+          <t>DYC 1L</t>
+        </is>
+      </c>
+      <c r="C296" s="11" t="n">
+        <v>10.68</v>
+      </c>
       <c r="D296" s="11" t="n"/>
-      <c r="E296" s="11" t="n">
-        <v>14.05</v>
-      </c>
+      <c r="E296" s="11" t="n"/>
       <c r="F296" s="11">
         <f>IF(D296&lt;&gt;"",D296,IF(C296&lt;&gt;"",C296,""))</f>
         <v/>
@@ -11781,11 +11785,7 @@
         <f>IF(AND(C296&lt;&gt;"",D296&lt;&gt;""),IF(C296=0,"",D296/C296-1),"")</f>
         <v/>
       </c>
-      <c r="K296" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 14,64 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K296" s="5" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="5" t="inlineStr">
@@ -11795,13 +11795,13 @@
       </c>
       <c r="B297" s="5" t="inlineStr">
         <is>
-          <t>FIREBALL 0.70</t>
+          <t>FERNET BRANCA 0,70L</t>
         </is>
       </c>
       <c r="C297" s="11" t="n"/>
       <c r="D297" s="11" t="n"/>
       <c r="E297" s="11" t="n">
-        <v>10.39</v>
+        <v>14.05</v>
       </c>
       <c r="F297" s="11">
         <f>IF(D297&lt;&gt;"",D297,IF(C297&lt;&gt;"",C297,""))</f>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="K297" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 10,82 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 14,64 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11837,13 +11837,13 @@
       </c>
       <c r="B298" s="5" t="inlineStr">
         <is>
-          <t>GIN MARTIN MILLERS 0,70L</t>
+          <t>FIREBALL 0.70</t>
         </is>
       </c>
       <c r="C298" s="11" t="n"/>
       <c r="D298" s="11" t="n"/>
       <c r="E298" s="11" t="n">
-        <v>17.91</v>
+        <v>10.39</v>
       </c>
       <c r="F298" s="11">
         <f>IF(D298&lt;&gt;"",D298,IF(C298&lt;&gt;"",C298,""))</f>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="K298" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 18,66 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 10,82 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11879,17 +11879,13 @@
       </c>
       <c r="B299" s="5" t="inlineStr">
         <is>
-          <t>GIN NORDÉS 0,70L</t>
-        </is>
-      </c>
-      <c r="C299" s="11" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="D299" s="11" t="n">
-        <v>19.1</v>
-      </c>
+          <t>GIN MARTIN MILLERS 0,70L</t>
+        </is>
+      </c>
+      <c r="C299" s="11" t="n"/>
+      <c r="D299" s="11" t="n"/>
       <c r="E299" s="11" t="n">
-        <v>19.1</v>
+        <v>17.91</v>
       </c>
       <c r="F299" s="11">
         <f>IF(D299&lt;&gt;"",D299,IF(C299&lt;&gt;"",C299,""))</f>
@@ -11913,7 +11909,7 @@
       </c>
       <c r="K299" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 19,90 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 18,66 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -11925,14 +11921,18 @@
       </c>
       <c r="B300" s="5" t="inlineStr">
         <is>
-          <t>GIN PUERTO INDIAS FRESA 0,70</t>
+          <t>GIN NORDÉS 0,70L</t>
         </is>
       </c>
       <c r="C300" s="11" t="n">
-        <v>13.18</v>
-      </c>
-      <c r="D300" s="11" t="n"/>
-      <c r="E300" s="11" t="n"/>
+        <v>19.1</v>
+      </c>
+      <c r="D300" s="11" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E300" s="11" t="n">
+        <v>19.1</v>
+      </c>
       <c r="F300" s="11">
         <f>IF(D300&lt;&gt;"",D300,IF(C300&lt;&gt;"",C300,""))</f>
         <v/>
@@ -11953,7 +11953,11 @@
         <f>IF(AND(C300&lt;&gt;"",D300&lt;&gt;""),IF(C300=0,"",D300/C300-1),"")</f>
         <v/>
       </c>
-      <c r="K300" s="5" t="n"/>
+      <c r="K300" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 19,90 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="5" t="inlineStr">
@@ -11963,13 +11967,13 @@
       </c>
       <c r="B301" s="5" t="inlineStr">
         <is>
-          <t>GREY GOOSE VODKA 0,70L NR</t>
-        </is>
-      </c>
-      <c r="C301" s="11" t="n"/>
-      <c r="D301" s="11" t="n">
-        <v>35.95</v>
-      </c>
+          <t>GIN PUERTO INDIAS FRESA 0,70</t>
+        </is>
+      </c>
+      <c r="C301" s="11" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="D301" s="11" t="n"/>
       <c r="E301" s="11" t="n"/>
       <c r="F301" s="11">
         <f>IF(D301&lt;&gt;"",D301,IF(C301&lt;&gt;"",C301,""))</f>
@@ -12001,13 +12005,13 @@
       </c>
       <c r="B302" s="5" t="inlineStr">
         <is>
-          <t>HAVANA 7 AÑOS NR</t>
-        </is>
-      </c>
-      <c r="C302" s="11" t="n">
-        <v>18.06</v>
-      </c>
-      <c r="D302" s="11" t="n"/>
+          <t>GREY GOOSE VODKA 0,70L NR</t>
+        </is>
+      </c>
+      <c r="C302" s="11" t="n"/>
+      <c r="D302" s="11" t="n">
+        <v>35.95</v>
+      </c>
       <c r="E302" s="11" t="n"/>
       <c r="F302" s="11">
         <f>IF(D302&lt;&gt;"",D302,IF(C302&lt;&gt;"",C302,""))</f>
@@ -12039,13 +12043,13 @@
       </c>
       <c r="B303" s="5" t="inlineStr">
         <is>
-          <t>HENDRICKS 0,70L</t>
-        </is>
-      </c>
-      <c r="C303" s="11" t="n"/>
-      <c r="D303" s="11" t="n">
-        <v>23.12</v>
-      </c>
+          <t>HAVANA 7 AÑOS NR</t>
+        </is>
+      </c>
+      <c r="C303" s="11" t="n">
+        <v>18.06</v>
+      </c>
+      <c r="D303" s="11" t="n"/>
       <c r="E303" s="11" t="n"/>
       <c r="F303" s="11">
         <f>IF(D303&lt;&gt;"",D303,IF(C303&lt;&gt;"",C303,""))</f>
@@ -12077,13 +12081,13 @@
       </c>
       <c r="B304" s="5" t="inlineStr">
         <is>
-          <t>HIERBAS 3 LITROS BEREMOT</t>
-        </is>
-      </c>
-      <c r="C304" s="11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="D304" s="11" t="n"/>
+          <t>HENDRICKS 0,70L</t>
+        </is>
+      </c>
+      <c r="C304" s="11" t="n"/>
+      <c r="D304" s="11" t="n">
+        <v>23.12</v>
+      </c>
       <c r="E304" s="11" t="n"/>
       <c r="F304" s="11">
         <f>IF(D304&lt;&gt;"",D304,IF(C304&lt;&gt;"",C304,""))</f>
@@ -12115,13 +12119,13 @@
       </c>
       <c r="B305" s="5" t="inlineStr">
         <is>
-          <t>HIERBAS 3L MOS DE PAS</t>
-        </is>
-      </c>
-      <c r="C305" s="11" t="n"/>
-      <c r="D305" s="11" t="n">
+          <t>HIERBAS 3 LITROS BEREMOT</t>
+        </is>
+      </c>
+      <c r="C305" s="11" t="n">
         <v>14.5</v>
       </c>
+      <c r="D305" s="11" t="n"/>
       <c r="E305" s="11" t="n"/>
       <c r="F305" s="11">
         <f>IF(D305&lt;&gt;"",D305,IF(C305&lt;&gt;"",C305,""))</f>
@@ -12153,13 +12157,13 @@
       </c>
       <c r="B306" s="5" t="inlineStr">
         <is>
-          <t>J. WALKER NEGRA 0,70L NR</t>
-        </is>
-      </c>
-      <c r="C306" s="11" t="n">
-        <v>21.42</v>
-      </c>
-      <c r="D306" s="11" t="n"/>
+          <t>HIERBAS 3L MOS DE PAS</t>
+        </is>
+      </c>
+      <c r="C306" s="11" t="n"/>
+      <c r="D306" s="11" t="n">
+        <v>14.5</v>
+      </c>
       <c r="E306" s="11" t="n"/>
       <c r="F306" s="11">
         <f>IF(D306&lt;&gt;"",D306,IF(C306&lt;&gt;"",C306,""))</f>
@@ -12191,11 +12195,11 @@
       </c>
       <c r="B307" s="5" t="inlineStr">
         <is>
-          <t>J. WALKER RED 0,70L NR</t>
+          <t>J. WALKER NEGRA 0,70L NR</t>
         </is>
       </c>
       <c r="C307" s="11" t="n">
-        <v>11.48</v>
+        <v>21.42</v>
       </c>
       <c r="D307" s="11" t="n"/>
       <c r="E307" s="11" t="n"/>
@@ -12229,14 +12233,14 @@
       </c>
       <c r="B308" s="5" t="inlineStr">
         <is>
-          <t>JAGERMEISTER L. HIERB 0,70L</t>
-        </is>
-      </c>
-      <c r="C308" s="11" t="n"/>
+          <t>J. WALKER RED 0,70L NR</t>
+        </is>
+      </c>
+      <c r="C308" s="11" t="n">
+        <v>11.48</v>
+      </c>
       <c r="D308" s="11" t="n"/>
-      <c r="E308" s="11" t="n">
-        <v>10.27</v>
-      </c>
+      <c r="E308" s="11" t="n"/>
       <c r="F308" s="11">
         <f>IF(D308&lt;&gt;"",D308,IF(C308&lt;&gt;"",C308,""))</f>
         <v/>
@@ -12257,11 +12261,7 @@
         <f>IF(AND(C308&lt;&gt;"",D308&lt;&gt;""),IF(C308=0,"",D308/C308-1),"")</f>
         <v/>
       </c>
-      <c r="K308" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 10,70 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K308" s="5" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="5" t="inlineStr">
@@ -12271,15 +12271,13 @@
       </c>
       <c r="B309" s="5" t="inlineStr">
         <is>
-          <t>JAMESON 0,70L</t>
+          <t>JAGERMEISTER L. HIERB 0,70L</t>
         </is>
       </c>
       <c r="C309" s="11" t="n"/>
-      <c r="D309" s="11" t="n">
-        <v>13.9</v>
-      </c>
+      <c r="D309" s="11" t="n"/>
       <c r="E309" s="11" t="n">
-        <v>13.9</v>
+        <v>10.27</v>
       </c>
       <c r="F309" s="11">
         <f>IF(D309&lt;&gt;"",D309,IF(C309&lt;&gt;"",C309,""))</f>
@@ -12303,7 +12301,7 @@
       </c>
       <c r="K309" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 14,48 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 10,70 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -12315,14 +12313,16 @@
       </c>
       <c r="B310" s="5" t="inlineStr">
         <is>
-          <t>JOSE CUERVO ESPECIAL 0,7L NR</t>
-        </is>
-      </c>
-      <c r="C310" s="11" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="D310" s="11" t="n"/>
-      <c r="E310" s="11" t="n"/>
+          <t>JAMESON 0,70L</t>
+        </is>
+      </c>
+      <c r="C310" s="11" t="n"/>
+      <c r="D310" s="11" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E310" s="11" t="n">
+        <v>13.9</v>
+      </c>
       <c r="F310" s="11">
         <f>IF(D310&lt;&gt;"",D310,IF(C310&lt;&gt;"",C310,""))</f>
         <v/>
@@ -12343,7 +12343,11 @@
         <f>IF(AND(C310&lt;&gt;"",D310&lt;&gt;""),IF(C310=0,"",D310/C310-1),"")</f>
         <v/>
       </c>
-      <c r="K310" s="5" t="n"/>
+      <c r="K310" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 14,48 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="5" t="inlineStr">
@@ -12353,16 +12357,14 @@
       </c>
       <c r="B311" s="5" t="inlineStr">
         <is>
-          <t>JOSE CUERVO SILVER 0.7</t>
+          <t>JOSE CUERVO ESPECIAL 0,7L NR</t>
         </is>
       </c>
       <c r="C311" s="11" t="n">
-        <v>12.17</v>
+        <v>13.11</v>
       </c>
       <c r="D311" s="11" t="n"/>
-      <c r="E311" s="11" t="n">
-        <v>12.17</v>
-      </c>
+      <c r="E311" s="11" t="n"/>
       <c r="F311" s="11">
         <f>IF(D311&lt;&gt;"",D311,IF(C311&lt;&gt;"",C311,""))</f>
         <v/>
@@ -12383,11 +12385,7 @@
         <f>IF(AND(C311&lt;&gt;"",D311&lt;&gt;""),IF(C311=0,"",D311/C311-1),"")</f>
         <v/>
       </c>
-      <c r="K311" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 12,68 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K311" s="5" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="5" t="inlineStr">
@@ -12397,16 +12395,16 @@
       </c>
       <c r="B312" s="5" t="inlineStr">
         <is>
-          <t>LARIOS 1L NR</t>
+          <t>JOSE CUERVO SILVER 0.7</t>
         </is>
       </c>
       <c r="C312" s="11" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="D312" s="11" t="n">
-        <v>9.91</v>
-      </c>
-      <c r="E312" s="11" t="n"/>
+        <v>12.17</v>
+      </c>
+      <c r="D312" s="11" t="n"/>
+      <c r="E312" s="11" t="n">
+        <v>12.17</v>
+      </c>
       <c r="F312" s="11">
         <f>IF(D312&lt;&gt;"",D312,IF(C312&lt;&gt;"",C312,""))</f>
         <v/>
@@ -12427,7 +12425,11 @@
         <f>IF(AND(C312&lt;&gt;"",D312&lt;&gt;""),IF(C312=0,"",D312/C312-1),"")</f>
         <v/>
       </c>
-      <c r="K312" s="5" t="n"/>
+      <c r="K312" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 12,68 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="5" t="inlineStr">
@@ -12437,13 +12439,15 @@
       </c>
       <c r="B313" s="5" t="inlineStr">
         <is>
-          <t>LARIOS ESPECIAL 12 NR</t>
+          <t>LARIOS 1L NR</t>
         </is>
       </c>
       <c r="C313" s="11" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="D313" s="11" t="n"/>
+        <v>9.91</v>
+      </c>
+      <c r="D313" s="11" t="n">
+        <v>9.91</v>
+      </c>
       <c r="E313" s="11" t="n"/>
       <c r="F313" s="11">
         <f>IF(D313&lt;&gt;"",D313,IF(C313&lt;&gt;"",C313,""))</f>
@@ -12475,11 +12479,11 @@
       </c>
       <c r="B314" s="5" t="inlineStr">
         <is>
-          <t>LICOR CAFÉ QUEMEIRAS 3L</t>
+          <t>LARIOS ESPECIAL 12 NR</t>
         </is>
       </c>
       <c r="C314" s="11" t="n">
-        <v>13.99</v>
+        <v>11.64</v>
       </c>
       <c r="D314" s="11" t="n"/>
       <c r="E314" s="11" t="n"/>
@@ -12513,15 +12517,13 @@
       </c>
       <c r="B315" s="5" t="inlineStr">
         <is>
-          <t>LIMONCELO DE 3L BEREMOT</t>
+          <t>LICOR CAFÉ QUEMEIRAS 3L</t>
         </is>
       </c>
       <c r="C315" s="11" t="n">
-        <v>15.32</v>
-      </c>
-      <c r="D315" s="11" t="n">
-        <v>15.32</v>
-      </c>
+        <v>13.99</v>
+      </c>
+      <c r="D315" s="11" t="n"/>
       <c r="E315" s="11" t="n"/>
       <c r="F315" s="11">
         <f>IF(D315&lt;&gt;"",D315,IF(C315&lt;&gt;"",C315,""))</f>
@@ -12553,13 +12555,15 @@
       </c>
       <c r="B316" s="5" t="inlineStr">
         <is>
-          <t>MACALLAN 12</t>
+          <t>LIMONCELO DE 3L BEREMOT</t>
         </is>
       </c>
       <c r="C316" s="11" t="n">
-        <v>53.77</v>
-      </c>
-      <c r="D316" s="11" t="n"/>
+        <v>15.32</v>
+      </c>
+      <c r="D316" s="11" t="n">
+        <v>15.32</v>
+      </c>
       <c r="E316" s="11" t="n"/>
       <c r="F316" s="11">
         <f>IF(D316&lt;&gt;"",D316,IF(C316&lt;&gt;"",C316,""))</f>
@@ -12591,18 +12595,14 @@
       </c>
       <c r="B317" s="5" t="inlineStr">
         <is>
-          <t>MAESTRO DOBEL DIAMANTE REPOSADO 0.70</t>
+          <t>MACALLAN 12</t>
         </is>
       </c>
       <c r="C317" s="11" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="D317" s="11" t="n">
-        <v>52.96</v>
-      </c>
-      <c r="E317" s="11" t="n">
-        <v>52.96</v>
-      </c>
+        <v>53.77</v>
+      </c>
+      <c r="D317" s="11" t="n"/>
+      <c r="E317" s="11" t="n"/>
       <c r="F317" s="11">
         <f>IF(D317&lt;&gt;"",D317,IF(C317&lt;&gt;"",C317,""))</f>
         <v/>
@@ -12623,11 +12623,7 @@
         <f>IF(AND(C317&lt;&gt;"",D317&lt;&gt;""),IF(C317=0,"",D317/C317-1),"")</f>
         <v/>
       </c>
-      <c r="K317" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 55,17 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K317" s="5" t="n"/>
     </row>
     <row r="318">
       <c r="A318" s="5" t="inlineStr">
@@ -12637,15 +12633,17 @@
       </c>
       <c r="B318" s="5" t="inlineStr">
         <is>
-          <t>MARTINI BLANCO 1L</t>
-        </is>
-      </c>
-      <c r="C318" s="11" t="n"/>
+          <t>MAESTRO DOBEL DIAMANTE REPOSADO 0.70</t>
+        </is>
+      </c>
+      <c r="C318" s="11" t="n">
+        <v>52.96</v>
+      </c>
       <c r="D318" s="11" t="n">
-        <v>8.029999999999999</v>
+        <v>52.96</v>
       </c>
       <c r="E318" s="11" t="n">
-        <v>8.029999999999999</v>
+        <v>52.96</v>
       </c>
       <c r="F318" s="11">
         <f>IF(D318&lt;&gt;"",D318,IF(C318&lt;&gt;"",C318,""))</f>
@@ -12669,7 +12667,7 @@
       </c>
       <c r="K318" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 8,36 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 55,17 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -12681,16 +12679,16 @@
       </c>
       <c r="B319" s="5" t="inlineStr">
         <is>
-          <t>MARTINI ROJO 1L</t>
-        </is>
-      </c>
-      <c r="C319" s="11" t="n">
-        <v>8.029999999999999</v>
-      </c>
+          <t>MARTINI BLANCO 1L</t>
+        </is>
+      </c>
+      <c r="C319" s="11" t="n"/>
       <c r="D319" s="11" t="n">
         <v>8.029999999999999</v>
       </c>
-      <c r="E319" s="11" t="n"/>
+      <c r="E319" s="11" t="n">
+        <v>8.029999999999999</v>
+      </c>
       <c r="F319" s="11">
         <f>IF(D319&lt;&gt;"",D319,IF(C319&lt;&gt;"",C319,""))</f>
         <v/>
@@ -12711,7 +12709,11 @@
         <f>IF(AND(C319&lt;&gt;"",D319&lt;&gt;""),IF(C319=0,"",D319/C319-1),"")</f>
         <v/>
       </c>
-      <c r="K319" s="5" t="n"/>
+      <c r="K319" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 8,36 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="5" t="inlineStr">
@@ -12721,12 +12723,14 @@
       </c>
       <c r="B320" s="5" t="inlineStr">
         <is>
-          <t>PACHARAN 3L MOS DE PAS</t>
-        </is>
-      </c>
-      <c r="C320" s="11" t="n"/>
+          <t>MARTINI ROJO 1L</t>
+        </is>
+      </c>
+      <c r="C320" s="11" t="n">
+        <v>8.029999999999999</v>
+      </c>
       <c r="D320" s="11" t="n">
-        <v>13.99</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="E320" s="11" t="n"/>
       <c r="F320" s="11">
@@ -12759,18 +12763,14 @@
       </c>
       <c r="B321" s="5" t="inlineStr">
         <is>
-          <t>RED BULL 24U</t>
-        </is>
-      </c>
-      <c r="C321" s="11" t="n">
-        <v>28.8</v>
-      </c>
+          <t>PACHARAN 3L MOS DE PAS</t>
+        </is>
+      </c>
+      <c r="C321" s="11" t="n"/>
       <c r="D321" s="11" t="n">
-        <v>36.86</v>
-      </c>
-      <c r="E321" s="11" t="n">
-        <v>36.86</v>
-      </c>
+        <v>13.99</v>
+      </c>
+      <c r="E321" s="11" t="n"/>
       <c r="F321" s="11">
         <f>IF(D321&lt;&gt;"",D321,IF(C321&lt;&gt;"",C321,""))</f>
         <v/>
@@ -12791,11 +12791,7 @@
         <f>IF(AND(C321&lt;&gt;"",D321&lt;&gt;""),IF(C321=0,"",D321/C321-1),"")</f>
         <v/>
       </c>
-      <c r="K321" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 38,40 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K321" s="5" t="n"/>
     </row>
     <row r="322">
       <c r="A322" s="5" t="inlineStr">
@@ -12805,14 +12801,18 @@
       </c>
       <c r="B322" s="5" t="inlineStr">
         <is>
-          <t>RED BULL LIGHT 24U</t>
-        </is>
-      </c>
-      <c r="C322" s="11" t="n"/>
+          <t>RED BULL 24U</t>
+        </is>
+      </c>
+      <c r="C322" s="11" t="n">
+        <v>28.8</v>
+      </c>
       <c r="D322" s="11" t="n">
         <v>36.86</v>
       </c>
-      <c r="E322" s="11" t="n"/>
+      <c r="E322" s="11" t="n">
+        <v>36.86</v>
+      </c>
       <c r="F322" s="11">
         <f>IF(D322&lt;&gt;"",D322,IF(C322&lt;&gt;"",C322,""))</f>
         <v/>
@@ -12833,7 +12833,11 @@
         <f>IF(AND(C322&lt;&gt;"",D322&lt;&gt;""),IF(C322=0,"",D322/C322-1),"")</f>
         <v/>
       </c>
-      <c r="K322" s="5" t="n"/>
+      <c r="K322" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 38,40 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="5" t="inlineStr">
@@ -12843,14 +12847,14 @@
       </c>
       <c r="B323" s="5" t="inlineStr">
         <is>
-          <t>RED BULL SANDIA 24U</t>
+          <t>RED BULL LIGHT 24U</t>
         </is>
       </c>
       <c r="C323" s="11" t="n"/>
-      <c r="D323" s="11" t="n"/>
-      <c r="E323" s="11" t="n">
+      <c r="D323" s="11" t="n">
         <v>36.86</v>
       </c>
+      <c r="E323" s="11" t="n"/>
       <c r="F323" s="11">
         <f>IF(D323&lt;&gt;"",D323,IF(C323&lt;&gt;"",C323,""))</f>
         <v/>
@@ -12871,11 +12875,7 @@
         <f>IF(AND(C323&lt;&gt;"",D323&lt;&gt;""),IF(C323=0,"",D323/C323-1),"")</f>
         <v/>
       </c>
-      <c r="K323" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 38,40 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K323" s="5" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="5" t="inlineStr">
@@ -12885,15 +12885,13 @@
       </c>
       <c r="B324" s="5" t="inlineStr">
         <is>
-          <t>RON BARCELO 0,70L NR</t>
-        </is>
-      </c>
-      <c r="C324" s="11" t="n">
-        <v>11.62</v>
-      </c>
+          <t>RED BULL SANDIA 24U</t>
+        </is>
+      </c>
+      <c r="C324" s="11" t="n"/>
       <c r="D324" s="11" t="n"/>
       <c r="E324" s="11" t="n">
-        <v>12.1</v>
+        <v>36.86</v>
       </c>
       <c r="F324" s="11">
         <f>IF(D324&lt;&gt;"",D324,IF(C324&lt;&gt;"",C324,""))</f>
@@ -12917,7 +12915,7 @@
       </c>
       <c r="K324" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 12,60 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 38,40 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -12929,14 +12927,16 @@
       </c>
       <c r="B325" s="5" t="inlineStr">
         <is>
-          <t>RON BARCELO IMPERIAL 0,70L</t>
+          <t>RON BARCELO 0,70L NR</t>
         </is>
       </c>
       <c r="C325" s="11" t="n">
-        <v>23.04</v>
+        <v>11.62</v>
       </c>
       <c r="D325" s="11" t="n"/>
-      <c r="E325" s="11" t="n"/>
+      <c r="E325" s="11" t="n">
+        <v>12.1</v>
+      </c>
       <c r="F325" s="11">
         <f>IF(D325&lt;&gt;"",D325,IF(C325&lt;&gt;"",C325,""))</f>
         <v/>
@@ -12957,7 +12957,11 @@
         <f>IF(AND(C325&lt;&gt;"",D325&lt;&gt;""),IF(C325=0,"",D325/C325-1),"")</f>
         <v/>
       </c>
-      <c r="K325" s="5" t="n"/>
+      <c r="K325" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 12,60 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="5" t="inlineStr">
@@ -12967,11 +12971,11 @@
       </c>
       <c r="B326" s="5" t="inlineStr">
         <is>
-          <t>RUINART BLANC DE BLANC 0,75</t>
+          <t>RON BARCELO IMPERIAL 0,70L</t>
         </is>
       </c>
       <c r="C326" s="11" t="n">
-        <v>69.58</v>
+        <v>23.04</v>
       </c>
       <c r="D326" s="11" t="n"/>
       <c r="E326" s="11" t="n"/>
@@ -13005,14 +13009,14 @@
       </c>
       <c r="B327" s="5" t="inlineStr">
         <is>
-          <t>SAINT GERMAIN</t>
-        </is>
-      </c>
-      <c r="C327" s="11" t="n"/>
+          <t>RUINART BLANC DE BLANC 0,75</t>
+        </is>
+      </c>
+      <c r="C327" s="11" t="n">
+        <v>69.58</v>
+      </c>
       <c r="D327" s="11" t="n"/>
-      <c r="E327" s="11" t="n">
-        <v>22.97</v>
-      </c>
+      <c r="E327" s="11" t="n"/>
       <c r="F327" s="11">
         <f>IF(D327&lt;&gt;"",D327,IF(C327&lt;&gt;"",C327,""))</f>
         <v/>
@@ -13033,11 +13037,7 @@
         <f>IF(AND(C327&lt;&gt;"",D327&lt;&gt;""),IF(C327=0,"",D327/C327-1),"")</f>
         <v/>
       </c>
-      <c r="K327" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 23,93 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K327" s="5" t="n"/>
     </row>
     <row r="328">
       <c r="A328" s="5" t="inlineStr">
@@ -13047,14 +13047,14 @@
       </c>
       <c r="B328" s="5" t="inlineStr">
         <is>
-          <t>SANTA TERESA G.RVA 0,70L</t>
-        </is>
-      </c>
-      <c r="C328" s="11" t="n">
-        <v>10.9</v>
-      </c>
+          <t>SAINT GERMAIN</t>
+        </is>
+      </c>
+      <c r="C328" s="11" t="n"/>
       <c r="D328" s="11" t="n"/>
-      <c r="E328" s="11" t="n"/>
+      <c r="E328" s="11" t="n">
+        <v>22.97</v>
+      </c>
       <c r="F328" s="11">
         <f>IF(D328&lt;&gt;"",D328,IF(C328&lt;&gt;"",C328,""))</f>
         <v/>
@@ -13075,7 +13075,11 @@
         <f>IF(AND(C328&lt;&gt;"",D328&lt;&gt;""),IF(C328=0,"",D328/C328-1),"")</f>
         <v/>
       </c>
-      <c r="K328" s="5" t="n"/>
+      <c r="K328" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 23,93 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="5" t="inlineStr">
@@ -13085,16 +13089,14 @@
       </c>
       <c r="B329" s="5" t="inlineStr">
         <is>
-          <t>SEAGRAMS 0,0 0,70L</t>
-        </is>
-      </c>
-      <c r="C329" s="11" t="n"/>
-      <c r="D329" s="11" t="n">
-        <v>12.47</v>
-      </c>
-      <c r="E329" s="11" t="n">
-        <v>12.47</v>
-      </c>
+          <t>SANTA TERESA G.RVA 0,70L</t>
+        </is>
+      </c>
+      <c r="C329" s="11" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="D329" s="11" t="n"/>
+      <c r="E329" s="11" t="n"/>
       <c r="F329" s="11">
         <f>IF(D329&lt;&gt;"",D329,IF(C329&lt;&gt;"",C329,""))</f>
         <v/>
@@ -13115,11 +13117,7 @@
         <f>IF(AND(C329&lt;&gt;"",D329&lt;&gt;""),IF(C329=0,"",D329/C329-1),"")</f>
         <v/>
       </c>
-      <c r="K329" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 12,99 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K329" s="5" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="5" t="inlineStr">
@@ -13129,15 +13127,15 @@
       </c>
       <c r="B330" s="5" t="inlineStr">
         <is>
-          <t>SEAGRAMS 0,70L NR</t>
-        </is>
-      </c>
-      <c r="C330" s="11" t="n">
-        <v>12.84</v>
-      </c>
-      <c r="D330" s="11" t="n"/>
+          <t>SEAGRAMS 0,0 0,70L</t>
+        </is>
+      </c>
+      <c r="C330" s="11" t="n"/>
+      <c r="D330" s="11" t="n">
+        <v>12.47</v>
+      </c>
       <c r="E330" s="11" t="n">
-        <v>12.84</v>
+        <v>12.47</v>
       </c>
       <c r="F330" s="11">
         <f>IF(D330&lt;&gt;"",D330,IF(C330&lt;&gt;"",C330,""))</f>
@@ -13161,7 +13159,7 @@
       </c>
       <c r="K330" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 13,38 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 12,99 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -13173,14 +13171,16 @@
       </c>
       <c r="B331" s="5" t="inlineStr">
         <is>
-          <t>TANQUERAY 0,70L</t>
-        </is>
-      </c>
-      <c r="C331" s="11" t="n"/>
-      <c r="D331" s="11" t="n">
-        <v>11.64</v>
-      </c>
-      <c r="E331" s="11" t="n"/>
+          <t>SEAGRAMS 0,70L NR</t>
+        </is>
+      </c>
+      <c r="C331" s="11" t="n">
+        <v>12.84</v>
+      </c>
+      <c r="D331" s="11" t="n"/>
+      <c r="E331" s="11" t="n">
+        <v>12.84</v>
+      </c>
       <c r="F331" s="11">
         <f>IF(D331&lt;&gt;"",D331,IF(C331&lt;&gt;"",C331,""))</f>
         <v/>
@@ -13201,7 +13201,11 @@
         <f>IF(AND(C331&lt;&gt;"",D331&lt;&gt;""),IF(C331=0,"",D331/C331-1),"")</f>
         <v/>
       </c>
-      <c r="K331" s="5" t="n"/>
+      <c r="K331" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 13,38 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="5" t="inlineStr">
@@ -13211,14 +13215,14 @@
       </c>
       <c r="B332" s="5" t="inlineStr">
         <is>
-          <t>TEQUILA DON JULIO 70 TH</t>
+          <t>TANQUERAY 0,70L</t>
         </is>
       </c>
       <c r="C332" s="11" t="n"/>
-      <c r="D332" s="11" t="n"/>
-      <c r="E332" s="11" t="n">
-        <v>58.99</v>
-      </c>
+      <c r="D332" s="11" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="E332" s="11" t="n"/>
       <c r="F332" s="11">
         <f>IF(D332&lt;&gt;"",D332,IF(C332&lt;&gt;"",C332,""))</f>
         <v/>
@@ -13239,11 +13243,7 @@
         <f>IF(AND(C332&lt;&gt;"",D332&lt;&gt;""),IF(C332=0,"",D332/C332-1),"")</f>
         <v/>
       </c>
-      <c r="K332" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 61,45 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K332" s="5" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="5" t="inlineStr">
@@ -13253,14 +13253,14 @@
       </c>
       <c r="B333" s="5" t="inlineStr">
         <is>
-          <t>WHITE LABEL 0,70L NR</t>
+          <t>TEQUILA DON JULIO 70 TH</t>
         </is>
       </c>
       <c r="C333" s="11" t="n"/>
-      <c r="D333" s="11" t="n">
-        <v>10.65</v>
-      </c>
-      <c r="E333" s="11" t="n"/>
+      <c r="D333" s="11" t="n"/>
+      <c r="E333" s="11" t="n">
+        <v>58.99</v>
+      </c>
       <c r="F333" s="11">
         <f>IF(D333&lt;&gt;"",D333,IF(C333&lt;&gt;"",C333,""))</f>
         <v/>
@@ -13281,7 +13281,11 @@
         <f>IF(AND(C333&lt;&gt;"",D333&lt;&gt;""),IF(C333=0,"",D333/C333-1),"")</f>
         <v/>
       </c>
-      <c r="K333" s="5" t="n"/>
+      <c r="K333" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 61,45 € con 4 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="5" t="inlineStr">
@@ -13291,14 +13295,14 @@
       </c>
       <c r="B334" s="5" t="inlineStr">
         <is>
-          <t>ZACAPA 23 AÑOS 0,70L</t>
+          <t>WHITE LABEL 0,70L NR</t>
         </is>
       </c>
       <c r="C334" s="11" t="n"/>
-      <c r="D334" s="11" t="n"/>
-      <c r="E334" s="11" t="n">
-        <v>28.62</v>
-      </c>
+      <c r="D334" s="11" t="n">
+        <v>10.65</v>
+      </c>
+      <c r="E334" s="11" t="n"/>
       <c r="F334" s="11">
         <f>IF(D334&lt;&gt;"",D334,IF(C334&lt;&gt;"",C334,""))</f>
         <v/>
@@ -13319,11 +13323,7 @@
         <f>IF(AND(C334&lt;&gt;"",D334&lt;&gt;""),IF(C334=0,"",D334/C334-1),"")</f>
         <v/>
       </c>
-      <c r="K334" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 29,81 € con 4 % de dto</t>
-        </is>
-      </c>
+      <c r="K334" s="5" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="5" t="inlineStr">
@@ -13333,13 +13333,13 @@
       </c>
       <c r="B335" s="5" t="inlineStr">
         <is>
-          <t>ZACAPA X.O.</t>
+          <t>ZACAPA 23 AÑOS 0,70L</t>
         </is>
       </c>
       <c r="C335" s="11" t="n"/>
       <c r="D335" s="11" t="n"/>
       <c r="E335" s="11" t="n">
-        <v>127.62</v>
+        <v>28.62</v>
       </c>
       <c r="F335" s="11">
         <f>IF(D335&lt;&gt;"",D335,IF(C335&lt;&gt;"",C335,""))</f>
@@ -13363,29 +13363,25 @@
       </c>
       <c r="K335" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 132,94 € con 4 % de dto</t>
+          <t>Precio neto: tarifa 29,81 € con 4 % de dto</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="5" t="inlineStr">
         <is>
-          <t>TOMATERIA DE CEA</t>
+          <t>SUBMARINER</t>
         </is>
       </c>
       <c r="B336" s="5" t="inlineStr">
         <is>
-          <t>RAF IBERICO</t>
-        </is>
-      </c>
-      <c r="C336" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="D336" s="11" t="n">
-        <v>6.5</v>
-      </c>
+          <t>ZACAPA X.O.</t>
+        </is>
+      </c>
+      <c r="C336" s="11" t="n"/>
+      <c r="D336" s="11" t="n"/>
       <c r="E336" s="11" t="n">
-        <v>6.5</v>
+        <v>127.62</v>
       </c>
       <c r="F336" s="11">
         <f>IF(D336&lt;&gt;"",D336,IF(C336&lt;&gt;"",C336,""))</f>
@@ -13409,7 +13405,7 @@
       </c>
       <c r="K336" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 6,00 / 6,50</t>
+          <t>Precio neto: tarifa 132,94 € con 4 % de dto</t>
         </is>
       </c>
     </row>
@@ -13421,11 +13417,15 @@
       </c>
       <c r="B337" s="5" t="inlineStr">
         <is>
-          <t>TOMATE MAR AZUL</t>
-        </is>
-      </c>
-      <c r="C337" s="11" t="n"/>
-      <c r="D337" s="11" t="n"/>
+          <t>RAF IBERICO</t>
+        </is>
+      </c>
+      <c r="C337" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="D337" s="11" t="n">
+        <v>6.5</v>
+      </c>
       <c r="E337" s="11" t="n">
         <v>6.5</v>
       </c>
@@ -13451,29 +13451,25 @@
       </c>
       <c r="K337" s="5" t="inlineStr">
         <is>
-          <t>Producto fresco: precio de mercado, fluctúa</t>
+          <t>Producto fresco: precio de mercado, fluctúa. Varios precios en agosto: 6,00 / 6,50</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="5" t="inlineStr">
         <is>
-          <t>VENERO CLARO</t>
+          <t>TOMATERIA DE CEA</t>
         </is>
       </c>
       <c r="B338" s="5" t="inlineStr">
         <is>
-          <t>LOMO VACA VENERO CLARO C/H</t>
-        </is>
-      </c>
-      <c r="C338" s="11" t="n">
-        <v>26</v>
-      </c>
-      <c r="D338" s="11" t="n">
-        <v>26</v>
-      </c>
+          <t>TOMATE MAR AZUL</t>
+        </is>
+      </c>
+      <c r="C338" s="11" t="n"/>
+      <c r="D338" s="11" t="n"/>
       <c r="E338" s="11" t="n">
-        <v>26</v>
+        <v>6.5</v>
       </c>
       <c r="F338" s="11">
         <f>IF(D338&lt;&gt;"",D338,IF(C338&lt;&gt;"",C338,""))</f>
@@ -13495,25 +13491,31 @@
         <f>IF(AND(C338&lt;&gt;"",D338&lt;&gt;""),IF(C338=0,"",D338/C338-1),"")</f>
         <v/>
       </c>
-      <c r="K338" s="5" t="n"/>
+      <c r="K338" s="5" t="inlineStr">
+        <is>
+          <t>Producto fresco: precio de mercado, fluctúa</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="5" t="inlineStr">
         <is>
-          <t>VINS DES DIEUX</t>
+          <t>VENERO CLARO</t>
         </is>
       </c>
       <c r="B339" s="5" t="inlineStr">
         <is>
-          <t>CANTALAPIEDRA CHIVIRITERO 2024</t>
+          <t>LOMO VACA VENERO CLARO C/H</t>
         </is>
       </c>
       <c r="C339" s="11" t="n">
-        <v>16.9</v>
-      </c>
-      <c r="D339" s="11" t="n"/>
+        <v>26</v>
+      </c>
+      <c r="D339" s="11" t="n">
+        <v>26</v>
+      </c>
       <c r="E339" s="11" t="n">
-        <v>15.55</v>
+        <v>26</v>
       </c>
       <c r="F339" s="11">
         <f>IF(D339&lt;&gt;"",D339,IF(C339&lt;&gt;"",C339,""))</f>
@@ -13535,11 +13537,7 @@
         <f>IF(AND(C339&lt;&gt;"",D339&lt;&gt;""),IF(C339=0,"",D339/C339-1),"")</f>
         <v/>
       </c>
-      <c r="K339" s="5" t="inlineStr">
-        <is>
-          <t>Precio neto: tarifa 16,90 € con 8 % de dto. OJO: cambia el dto. (julio 0 %, septiembre 8 %)</t>
-        </is>
-      </c>
+      <c r="K339" s="5" t="n"/>
     </row>
     <row r="340">
       <c r="A340" s="5" t="inlineStr">
@@ -13549,13 +13547,15 @@
       </c>
       <c r="B340" s="5" t="inlineStr">
         <is>
-          <t>CHAMPAGNE CHAVOST BLANC D'ASSEMBLAGE BRUT NATURE</t>
-        </is>
-      </c>
-      <c r="C340" s="11" t="n"/>
+          <t>CANTALAPIEDRA CHIVIRITERO 2024</t>
+        </is>
+      </c>
+      <c r="C340" s="11" t="n">
+        <v>16.9</v>
+      </c>
       <c r="D340" s="11" t="n"/>
       <c r="E340" s="11" t="n">
-        <v>28.43</v>
+        <v>15.55</v>
       </c>
       <c r="F340" s="11">
         <f>IF(D340&lt;&gt;"",D340,IF(C340&lt;&gt;"",C340,""))</f>
@@ -13579,27 +13579,25 @@
       </c>
       <c r="K340" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 30,90 € con 8 % de dto</t>
+          <t>Precio neto: tarifa 16,90 € con 8 % de dto. OJO: cambia el dto. (julio 0 %, septiembre 8 %)</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="5" t="inlineStr">
         <is>
-          <t>VOLDIS</t>
+          <t>VINS DES DIEUX</t>
         </is>
       </c>
       <c r="B341" s="5" t="inlineStr">
         <is>
-          <t>AGUA CON GAS SOLAN DE CABRAS VIDRIO RNR 33CL</t>
-        </is>
-      </c>
-      <c r="C341" s="11" t="n">
-        <v>16.09</v>
-      </c>
+          <t>CHAMPAGNE CHAVOST BLANC D'ASSEMBLAGE BRUT NATURE</t>
+        </is>
+      </c>
+      <c r="C341" s="11" t="n"/>
       <c r="D341" s="11" t="n"/>
       <c r="E341" s="11" t="n">
-        <v>16.09</v>
+        <v>28.43</v>
       </c>
       <c r="F341" s="11">
         <f>IF(D341&lt;&gt;"",D341,IF(C341&lt;&gt;"",C341,""))</f>
@@ -13623,7 +13621,7 @@
       </c>
       <c r="K341" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 26,81 € con 40 % de dto</t>
+          <t>Precio neto: tarifa 30,90 € con 8 % de dto</t>
         </is>
       </c>
     </row>
@@ -13635,15 +13633,15 @@
       </c>
       <c r="B342" s="5" t="inlineStr">
         <is>
-          <t>AGUA SOLAN DE CABRAS VIDRIO RET 50CL 20U</t>
+          <t>AGUA CON GAS SOLAN DE CABRAS VIDRIO RNR 33CL</t>
         </is>
       </c>
       <c r="C342" s="11" t="n">
-        <v>7.38</v>
+        <v>16.09</v>
       </c>
       <c r="D342" s="11" t="n"/>
       <c r="E342" s="11" t="n">
-        <v>7.38</v>
+        <v>16.09</v>
       </c>
       <c r="F342" s="11">
         <f>IF(D342&lt;&gt;"",D342,IF(C342&lt;&gt;"",C342,""))</f>
@@ -13667,7 +13665,7 @@
       </c>
       <c r="K342" s="5" t="inlineStr">
         <is>
-          <t>Precio neto: tarifa 12,30 € con 40 % de dto</t>
+          <t>Precio neto: tarifa 26,81 € con 40 % de dto</t>
         </is>
       </c>
     </row>
@@ -13679,15 +13677,15 @@
       </c>
       <c r="B343" s="5" t="inlineStr">
         <is>
-          <t>ALHAMBRA RESERVA 1925 VIDRIO NR 33CL</t>
+          <t>AGUA SOLAN DE CABRAS VIDRIO RET 50CL 20U</t>
         </is>
       </c>
       <c r="C343" s="11" t="n">
-        <v>41.92</v>
+        <v>7.38</v>
       </c>
       <c r="D343" s="11" t="n"/>
       <c r="E343" s="11" t="n">
-        <v>41.92</v>
+        <v>7.38</v>
       </c>
       <c r="F343" s="11">
         <f>IF(D343&lt;&gt;"",D343,IF(C343&lt;&gt;"",C343,""))</f>
@@ -13709,7 +13707,11 @@
         <f>IF(AND(C343&lt;&gt;"",D343&lt;&gt;""),IF(C343=0,"",D343/C343-1),"")</f>
         <v/>
       </c>
-      <c r="K343" s="5" t="n"/>
+      <c r="K343" s="5" t="inlineStr">
+        <is>
+          <t>Precio neto: tarifa 12,30 € con 40 % de dto</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="5" t="inlineStr">
@@ -13719,15 +13721,15 @@
       </c>
       <c r="B344" s="5" t="inlineStr">
         <is>
-          <t>AQUARADE ZERO LIMON VIDRIO RET 35CL</t>
+          <t>ALHAMBRA RESERVA 1925 VIDRIO NR 33CL</t>
         </is>
       </c>
       <c r="C344" s="11" t="n">
-        <v>33.54</v>
+        <v>41.92</v>
       </c>
       <c r="D344" s="11" t="n"/>
       <c r="E344" s="11" t="n">
-        <v>33.84</v>
+        <v>41.92</v>
       </c>
       <c r="F344" s="11">
         <f>IF(D344&lt;&gt;"",D344,IF(C344&lt;&gt;"",C344,""))</f>
@@ -13759,14 +13761,16 @@
       </c>
       <c r="B345" s="5" t="inlineStr">
         <is>
-          <t>AQUARADE ZERO NARANJA VIDRIO RET 35CL</t>
+          <t>AQUARADE ZERO LIMON VIDRIO RET 35CL</t>
         </is>
       </c>
       <c r="C345" s="11" t="n">
+        <v>33.54</v>
+      </c>
+      <c r="D345" s="11" t="n"/>
+      <c r="E345" s="11" t="n">
         <v>33.84</v>
       </c>
-      <c r="D345" s="11" t="n"/>
-      <c r="E345" s="11" t="n"/>
       <c r="F345" s="11">
         <f>IF(D345&lt;&gt;"",D345,IF(C345&lt;&gt;"",C345,""))</f>
         <v/>
@@ -13797,14 +13801,16 @@
       </c>
       <c r="B346" s="5" t="inlineStr">
         <is>
-          <t>LA CASERA GASEOSA PET 1L CAJA 12U</t>
+          <t>AQUARADE ZERO NARANJA VIDRIO RET 35CL</t>
         </is>
       </c>
       <c r="C346" s="11" t="n">
-        <v>21.48</v>
+        <v>33.84</v>
       </c>
       <c r="D346" s="11" t="n"/>
-      <c r="E346" s="11" t="n"/>
+      <c r="E346" s="11" t="n">
+        <v>33.84</v>
+      </c>
       <c r="F346" s="11">
         <f>IF(D346&lt;&gt;"",D346,IF(C346&lt;&gt;"",C346,""))</f>
         <v/>
@@ -13835,14 +13841,14 @@
       </c>
       <c r="B347" s="5" t="inlineStr">
         <is>
-          <t>LA CASERA GASEOSA PET 50CL CAJA 12U</t>
-        </is>
-      </c>
-      <c r="C347" s="11" t="n"/>
+          <t>LA CASERA GASEOSA PET 1L CAJA 12U</t>
+        </is>
+      </c>
+      <c r="C347" s="11" t="n">
+        <v>21.48</v>
+      </c>
       <c r="D347" s="11" t="n"/>
-      <c r="E347" s="11" t="n">
-        <v>15.96</v>
-      </c>
+      <c r="E347" s="11" t="n"/>
       <c r="F347" s="11">
         <f>IF(D347&lt;&gt;"",D347,IF(C347&lt;&gt;"",C347,""))</f>
         <v/>
@@ -13873,15 +13879,13 @@
       </c>
       <c r="B348" s="5" t="inlineStr">
         <is>
-          <t>LA CASERA LIMON PET 1L CAJA 12U</t>
-        </is>
-      </c>
-      <c r="C348" s="11" t="n">
-        <v>24.61</v>
-      </c>
+          <t>LA CASERA GASEOSA PET 50CL CAJA 12U</t>
+        </is>
+      </c>
+      <c r="C348" s="11" t="n"/>
       <c r="D348" s="11" t="n"/>
       <c r="E348" s="11" t="n">
-        <v>24.61</v>
+        <v>15.96</v>
       </c>
       <c r="F348" s="11">
         <f>IF(D348&lt;&gt;"",D348,IF(C348&lt;&gt;"",C348,""))</f>
@@ -13913,15 +13917,15 @@
       </c>
       <c r="B349" s="5" t="inlineStr">
         <is>
-          <t>LIPTON ZERO LIMON VIDRIO RET 35CL CAJA 24U</t>
+          <t>LA CASERA LIMON PET 1L CAJA 12U</t>
         </is>
       </c>
       <c r="C349" s="11" t="n">
-        <v>32.88</v>
+        <v>24.61</v>
       </c>
       <c r="D349" s="11" t="n"/>
       <c r="E349" s="11" t="n">
-        <v>32.88</v>
+        <v>24.61</v>
       </c>
       <c r="F349" s="11">
         <f>IF(D349&lt;&gt;"",D349,IF(C349&lt;&gt;"",C349,""))</f>
@@ -13953,15 +13957,15 @@
       </c>
       <c r="B350" s="5" t="inlineStr">
         <is>
-          <t>MAHOU 0,0 TOSTADA VIDRIO RET 33CL</t>
+          <t>LIPTON ZERO LIMON VIDRIO RET 35CL CAJA 24U</t>
         </is>
       </c>
       <c r="C350" s="11" t="n">
-        <v>38.3</v>
+        <v>32.88</v>
       </c>
       <c r="D350" s="11" t="n"/>
       <c r="E350" s="11" t="n">
-        <v>38.3</v>
+        <v>32.88</v>
       </c>
       <c r="F350" s="11">
         <f>IF(D350&lt;&gt;"",D350,IF(C350&lt;&gt;"",C350,""))</f>
@@ -13993,15 +13997,15 @@
       </c>
       <c r="B351" s="5" t="inlineStr">
         <is>
-          <t>MAHOU 5 ESTRELLAS SIN GLUTEN VIDRIO NR 33CL</t>
+          <t>MAHOU 0,0 TOSTADA VIDRIO RET 33CL</t>
         </is>
       </c>
       <c r="C351" s="11" t="n">
-        <v>45.52</v>
+        <v>38.3</v>
       </c>
       <c r="D351" s="11" t="n"/>
       <c r="E351" s="11" t="n">
-        <v>45.52</v>
+        <v>38.3</v>
       </c>
       <c r="F351" s="11">
         <f>IF(D351&lt;&gt;"",D351,IF(C351&lt;&gt;"",C351,""))</f>
@@ -14033,15 +14037,15 @@
       </c>
       <c r="B352" s="5" t="inlineStr">
         <is>
-          <t>MAHOU 5 ESTRELLAS VIDRIO RET 33CL CAJA 24U</t>
+          <t>MAHOU 5 ESTRELLAS SIN GLUTEN VIDRIO NR 33CL</t>
         </is>
       </c>
       <c r="C352" s="11" t="n">
-        <v>31.26</v>
+        <v>45.52</v>
       </c>
       <c r="D352" s="11" t="n"/>
       <c r="E352" s="11" t="n">
-        <v>31.27</v>
+        <v>45.52</v>
       </c>
       <c r="F352" s="11">
         <f>IF(D352&lt;&gt;"",D352,IF(C352&lt;&gt;"",C352,""))</f>
@@ -14073,15 +14077,15 @@
       </c>
       <c r="B353" s="5" t="inlineStr">
         <is>
-          <t>MAHOU SIN BARRIL RET 10L</t>
+          <t>MAHOU 5 ESTRELLAS VIDRIO RET 33CL CAJA 24U</t>
         </is>
       </c>
       <c r="C353" s="11" t="n">
-        <v>46.21</v>
+        <v>31.26</v>
       </c>
       <c r="D353" s="11" t="n"/>
       <c r="E353" s="11" t="n">
-        <v>46.21</v>
+        <v>31.27</v>
       </c>
       <c r="F353" s="11">
         <f>IF(D353&lt;&gt;"",D353,IF(C353&lt;&gt;"",C353,""))</f>
@@ -14113,15 +14117,15 @@
       </c>
       <c r="B354" s="5" t="inlineStr">
         <is>
-          <t>SCHWEPPES GINGER ALE LOW CAL VIDRIO RET 20CL CAJA 28 U</t>
+          <t>MAHOU SIN BARRIL RET 10L</t>
         </is>
       </c>
       <c r="C354" s="11" t="n">
-        <v>31.92</v>
+        <v>46.21</v>
       </c>
       <c r="D354" s="11" t="n"/>
       <c r="E354" s="11" t="n">
-        <v>31.92</v>
+        <v>46.21</v>
       </c>
       <c r="F354" s="11">
         <f>IF(D354&lt;&gt;"",D354,IF(C354&lt;&gt;"",C354,""))</f>
@@ -14153,14 +14157,16 @@
       </c>
       <c r="B355" s="5" t="inlineStr">
         <is>
-          <t>SCHWEPPES LIMON LOW CAL VIDRIO RET 20CL</t>
+          <t>SCHWEPPES GINGER ALE LOW CAL VIDRIO RET 20CL CAJA 28 U</t>
         </is>
       </c>
       <c r="C355" s="11" t="n">
-        <v>26.04</v>
+        <v>31.92</v>
       </c>
       <c r="D355" s="11" t="n"/>
-      <c r="E355" s="11" t="n"/>
+      <c r="E355" s="11" t="n">
+        <v>31.92</v>
+      </c>
       <c r="F355" s="11">
         <f>IF(D355&lt;&gt;"",D355,IF(C355&lt;&gt;"",C355,""))</f>
         <v/>
@@ -14191,14 +14197,16 @@
       </c>
       <c r="B356" s="5" t="inlineStr">
         <is>
-          <t>SCHWEPPES NARANJA LOW CAL VIDRIO RET 20CL</t>
+          <t>SCHWEPPES LIMON LOW CAL VIDRIO RET 20CL</t>
         </is>
       </c>
       <c r="C356" s="11" t="n">
         <v>26.04</v>
       </c>
       <c r="D356" s="11" t="n"/>
-      <c r="E356" s="11" t="n"/>
+      <c r="E356" s="11" t="n">
+        <v>26.04</v>
+      </c>
       <c r="F356" s="11">
         <f>IF(D356&lt;&gt;"",D356,IF(C356&lt;&gt;"",C356,""))</f>
         <v/>
@@ -14229,13 +14237,15 @@
       </c>
       <c r="B357" s="5" t="inlineStr">
         <is>
-          <t>SCHWEPPES SELECTION GINGER BEER VIDRIO NR 20CL</t>
-        </is>
-      </c>
-      <c r="C357" s="11" t="n"/>
+          <t>SCHWEPPES NARANJA LOW CAL VIDRIO RET 20CL</t>
+        </is>
+      </c>
+      <c r="C357" s="11" t="n">
+        <v>26.04</v>
+      </c>
       <c r="D357" s="11" t="n"/>
       <c r="E357" s="11" t="n">
-        <v>23.28</v>
+        <v>26.04</v>
       </c>
       <c r="F357" s="11">
         <f>IF(D357&lt;&gt;"",D357,IF(C357&lt;&gt;"",C357,""))</f>
@@ -14267,14 +14277,14 @@
       </c>
       <c r="B358" s="5" t="inlineStr">
         <is>
-          <t>SCHWEPPES TONICA VIDRIO RET 20CL CAJA 28U</t>
-        </is>
-      </c>
-      <c r="C358" s="11" t="n">
-        <v>31.92</v>
-      </c>
+          <t>SCHWEPPES SELECTION GINGER BEER VIDRIO NR 20CL</t>
+        </is>
+      </c>
+      <c r="C358" s="11" t="n"/>
       <c r="D358" s="11" t="n"/>
-      <c r="E358" s="11" t="n"/>
+      <c r="E358" s="11" t="n">
+        <v>23.28</v>
+      </c>
       <c r="F358" s="11">
         <f>IF(D358&lt;&gt;"",D358,IF(C358&lt;&gt;"",C358,""))</f>
         <v/>
@@ -14305,15 +14315,15 @@
       </c>
       <c r="B359" s="5" t="inlineStr">
         <is>
-          <t>SEVEN UP ZERO AXL VIDRIO RET 20CL</t>
+          <t>SCHWEPPES TONICA VIDRIO RET 20CL CAJA 28U</t>
         </is>
       </c>
       <c r="C359" s="11" t="n">
-        <v>23.28</v>
+        <v>31.92</v>
       </c>
       <c r="D359" s="11" t="n"/>
       <c r="E359" s="11" t="n">
-        <v>23.28</v>
+        <v>31.92</v>
       </c>
       <c r="F359" s="11">
         <f>IF(D359&lt;&gt;"",D359,IF(C359&lt;&gt;"",C359,""))</f>
@@ -14345,13 +14355,15 @@
       </c>
       <c r="B360" s="5" t="inlineStr">
         <is>
-          <t>ZUMO VIDA MELOCOTON VIDRIO NR 20CL</t>
-        </is>
-      </c>
-      <c r="C360" s="11" t="n"/>
+          <t>SEVEN UP ZERO AXL VIDRIO RET 20CL</t>
+        </is>
+      </c>
+      <c r="C360" s="11" t="n">
+        <v>23.28</v>
+      </c>
       <c r="D360" s="11" t="n"/>
       <c r="E360" s="11" t="n">
-        <v>29.91</v>
+        <v>23.28</v>
       </c>
       <c r="F360" s="11">
         <f>IF(D360&lt;&gt;"",D360,IF(C360&lt;&gt;"",C360,""))</f>
@@ -14383,12 +14395,10 @@
       </c>
       <c r="B361" s="5" t="inlineStr">
         <is>
-          <t>ZUMO VIDA NARANJA VIDRIO NR 20CL</t>
-        </is>
-      </c>
-      <c r="C361" s="11" t="n">
-        <v>29.91</v>
-      </c>
+          <t>ZUMO VIDA MELOCOTON VIDRIO NR 20CL</t>
+        </is>
+      </c>
+      <c r="C361" s="11" t="n"/>
       <c r="D361" s="11" t="n"/>
       <c r="E361" s="11" t="n">
         <v>29.91</v>
@@ -14423,14 +14433,16 @@
       </c>
       <c r="B362" s="5" t="inlineStr">
         <is>
-          <t>ZUMO VIDA PIÑA VIDRIO NR 20CL</t>
+          <t>ZUMO VIDA NARANJA VIDRIO NR 20CL</t>
         </is>
       </c>
       <c r="C362" s="11" t="n">
         <v>29.91</v>
       </c>
       <c r="D362" s="11" t="n"/>
-      <c r="E362" s="11" t="n"/>
+      <c r="E362" s="11" t="n">
+        <v>29.91</v>
+      </c>
       <c r="F362" s="11">
         <f>IF(D362&lt;&gt;"",D362,IF(C362&lt;&gt;"",C362,""))</f>
         <v/>
@@ -14453,8 +14465,84 @@
       </c>
       <c r="K362" s="5" t="n"/>
     </row>
+    <row r="363">
+      <c r="A363" s="5" t="inlineStr">
+        <is>
+          <t>VOLDIS</t>
+        </is>
+      </c>
+      <c r="B363" s="5" t="inlineStr">
+        <is>
+          <t>ZUMO VIDA PIÑA VIDRIO NR 20CL</t>
+        </is>
+      </c>
+      <c r="C363" s="11" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="D363" s="11" t="n"/>
+      <c r="E363" s="11" t="n"/>
+      <c r="F363" s="11">
+        <f>IF(D363&lt;&gt;"",D363,IF(C363&lt;&gt;"",C363,""))</f>
+        <v/>
+      </c>
+      <c r="G363" s="11">
+        <f>IF(AND(E363&lt;&gt;"",F363&lt;&gt;""),E363-F363,"")</f>
+        <v/>
+      </c>
+      <c r="H363" s="17">
+        <f>IF(G363="","",IF(F363=0,"",G363/F363))</f>
+        <v/>
+      </c>
+      <c r="I363" s="18">
+        <f>IF(E363="","SIN COMPRA",IF(F363="","NUEVO",IF(AND(ABS(G363)&lt;0.015,ABS(G363)&lt;F363*0.005),"IGUAL",IF(G363&gt;0,"SUBE","BAJA"))))</f>
+        <v/>
+      </c>
+      <c r="J363" s="17">
+        <f>IF(AND(C363&lt;&gt;"",D363&lt;&gt;""),IF(C363=0,"",D363/C363-1),"")</f>
+        <v/>
+      </c>
+      <c r="K363" s="5" t="n"/>
+    </row>
+    <row r="364">
+      <c r="A364" s="5" t="inlineStr">
+        <is>
+          <t>VOLDIS</t>
+        </is>
+      </c>
+      <c r="B364" s="5" t="inlineStr">
+        <is>
+          <t>ZUMO VIDA TOMATE VIDRIO NR 20CL</t>
+        </is>
+      </c>
+      <c r="C364" s="11" t="n"/>
+      <c r="D364" s="11" t="n"/>
+      <c r="E364" s="11" t="n">
+        <v>29.91</v>
+      </c>
+      <c r="F364" s="11">
+        <f>IF(D364&lt;&gt;"",D364,IF(C364&lt;&gt;"",C364,""))</f>
+        <v/>
+      </c>
+      <c r="G364" s="11">
+        <f>IF(AND(E364&lt;&gt;"",F364&lt;&gt;""),E364-F364,"")</f>
+        <v/>
+      </c>
+      <c r="H364" s="17">
+        <f>IF(G364="","",IF(F364=0,"",G364/F364))</f>
+        <v/>
+      </c>
+      <c r="I364" s="18">
+        <f>IF(E364="","SIN COMPRA",IF(F364="","NUEVO",IF(AND(ABS(G364)&lt;0.015,ABS(G364)&lt;F364*0.005),"IGUAL",IF(G364&gt;0,"SUBE","BAJA"))))</f>
+        <v/>
+      </c>
+      <c r="J364" s="17">
+        <f>IF(AND(C364&lt;&gt;"",D364&lt;&gt;""),IF(C364=0,"",D364/C364-1),"")</f>
+        <v/>
+      </c>
+      <c r="K364" s="5" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A55:K362"/>
+  <autoFilter ref="A55:K364"/>
   <mergeCells count="31">
     <mergeCell ref="G43:K43"/>
     <mergeCell ref="A30:K30"/>
@@ -14488,7 +14576,7 @@
     <mergeCell ref="G46:K46"/>
     <mergeCell ref="G40:K40"/>
   </mergeCells>
-  <conditionalFormatting sqref="I56:I362">
+  <conditionalFormatting sqref="I56:I364">
     <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
       <formula>"SUBE"</formula>
     </cfRule>
@@ -14502,7 +14590,7 @@
       <formula>"SIN COMPRA"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J56:J362">
+  <conditionalFormatting sqref="J56:J364">
     <cfRule type="expression" priority="5" dxfId="4">
       <formula>AND(ISNUMBER(J56),J56&gt;0.00001)</formula>
     </cfRule>
